--- a/outputs/shipment_summary.xlsx
+++ b/outputs/shipment_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="8">
   <si>
     <t>From</t>
   </si>
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -417,13 +417,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
+        <v>4104</v>
+      </c>
+      <c r="B2">
         <v>2000</v>
       </c>
-      <c r="B2">
-        <v>4200</v>
-      </c>
       <c r="C2">
-        <v>4679.19</v>
+        <v>954.96</v>
       </c>
       <c r="D2">
         <v>189</v>
@@ -434,13 +434,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>2000</v>
+        <v>4104</v>
       </c>
       <c r="B3">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="C3">
-        <v>6216.41</v>
+        <v>1915.22</v>
       </c>
       <c r="D3">
         <v>189</v>
@@ -451,13 +451,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>2000</v>
+        <v>4104</v>
       </c>
       <c r="B4">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="C4">
-        <v>20364.52</v>
+        <v>947.85</v>
       </c>
       <c r="D4">
         <v>189</v>
@@ -468,13 +468,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>2000</v>
+        <v>4201</v>
       </c>
       <c r="B5">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C5">
-        <v>2521.22</v>
+        <v>1860.76</v>
       </c>
       <c r="D5">
         <v>189</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>4104</v>
+        <v>4201</v>
       </c>
       <c r="B6">
-        <v>4200</v>
+        <v>4403</v>
       </c>
       <c r="C6">
-        <v>5078.03</v>
+        <v>5867.06</v>
       </c>
       <c r="D6">
         <v>189</v>
@@ -502,13 +502,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>4108</v>
+        <v>4201</v>
       </c>
       <c r="B7">
-        <v>4101</v>
+        <v>4404</v>
       </c>
       <c r="C7">
-        <v>22551.59</v>
+        <v>1198.21</v>
       </c>
       <c r="D7">
         <v>189</v>
@@ -519,13 +519,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B8">
-        <v>4105</v>
+        <v>4404</v>
       </c>
       <c r="C8">
-        <v>1530.09</v>
+        <v>6482.03</v>
       </c>
       <c r="D8">
         <v>189</v>
@@ -536,16 +536,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B9">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="C9">
-        <v>13255.62</v>
+        <v>2441.61</v>
       </c>
       <c r="D9">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -553,16 +553,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B10">
         <v>4401</v>
       </c>
       <c r="C10">
-        <v>12276.16</v>
+        <v>1081.7</v>
       </c>
       <c r="D10">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -570,16 +570,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B11">
         <v>4403</v>
       </c>
       <c r="C11">
-        <v>15008.39</v>
+        <v>439.2</v>
       </c>
       <c r="D11">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -587,16 +587,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>4201</v>
+        <v>4105</v>
       </c>
       <c r="B12">
-        <v>4200</v>
+        <v>4403</v>
       </c>
       <c r="C12">
-        <v>8926.040000000001</v>
+        <v>979.4400000000001</v>
       </c>
       <c r="D12">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -604,16 +604,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>4302</v>
+        <v>4108</v>
       </c>
       <c r="B13">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C13">
-        <v>3330.67</v>
+        <v>74.69</v>
       </c>
       <c r="D13">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -621,16 +621,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>4400</v>
+        <v>4108</v>
       </c>
       <c r="B14">
-        <v>4401</v>
+        <v>4404</v>
       </c>
       <c r="C14">
-        <v>8773.26</v>
+        <v>846.67</v>
       </c>
       <c r="D14">
-        <v>189</v>
+        <v>1167</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -638,13 +638,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B15">
-        <v>4101</v>
+        <v>4401</v>
       </c>
       <c r="C15">
-        <v>348.52</v>
+        <v>682.47</v>
       </c>
       <c r="D15">
         <v>1167</v>
@@ -655,13 +655,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B16">
         <v>4403</v>
       </c>
       <c r="C16">
-        <v>1072.46</v>
+        <v>220.42</v>
       </c>
       <c r="D16">
         <v>1167</v>
@@ -672,16 +672,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>4108</v>
+        <v>4201</v>
       </c>
       <c r="B17">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C17">
-        <v>698.04</v>
+        <v>1937.03</v>
       </c>
       <c r="D17">
-        <v>1296</v>
+        <v>1167</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -689,16 +689,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B18">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="C18">
-        <v>19.24</v>
+        <v>563.35</v>
       </c>
       <c r="D18">
-        <v>1296</v>
+        <v>1167</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>4301</v>
+        <v>4302</v>
       </c>
       <c r="B19">
-        <v>2000</v>
+        <v>4403</v>
       </c>
       <c r="C19">
-        <v>385.14</v>
+        <v>463.82</v>
       </c>
       <c r="D19">
-        <v>1296</v>
+        <v>1167</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -723,16 +723,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="B20">
-        <v>4100</v>
+        <v>4403</v>
       </c>
       <c r="C20">
-        <v>207.92</v>
+        <v>245.63</v>
       </c>
       <c r="D20">
-        <v>2122</v>
+        <v>1167</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -740,16 +740,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B21">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C21">
-        <v>936.54</v>
+        <v>43.81</v>
       </c>
       <c r="D21">
-        <v>2122</v>
+        <v>1167</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
@@ -757,16 +757,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>4301</v>
+        <v>4104</v>
       </c>
       <c r="B22">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="C22">
-        <v>14583.97</v>
+        <v>110.4</v>
       </c>
       <c r="D22">
-        <v>2122</v>
+        <v>1296</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -774,19 +774,19 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>4108</v>
+        <v>4105</v>
       </c>
       <c r="B23">
         <v>4101</v>
       </c>
       <c r="C23">
-        <v>160.79</v>
+        <v>23.21</v>
       </c>
       <c r="D23">
-        <v>4145</v>
+        <v>1296</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -794,16 +794,16 @@
         <v>4108</v>
       </c>
       <c r="B24">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="C24">
-        <v>477</v>
+        <v>301.15</v>
       </c>
       <c r="D24">
-        <v>4145</v>
+        <v>1296</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -811,30 +811,30 @@
         <v>4108</v>
       </c>
       <c r="B25">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C25">
-        <v>106.66</v>
+        <v>530.83</v>
       </c>
       <c r="D25">
-        <v>4145</v>
+        <v>1296</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>4105</v>
+        <v>4302</v>
       </c>
       <c r="B26">
-        <v>4404</v>
+        <v>2000</v>
       </c>
       <c r="C26">
-        <v>11.81</v>
+        <v>271.19</v>
       </c>
       <c r="D26">
-        <v>5159</v>
+        <v>1296</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -842,16 +842,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="B27">
-        <v>4404</v>
+        <v>2000</v>
       </c>
       <c r="C27">
-        <v>7.2</v>
+        <v>113.95</v>
       </c>
       <c r="D27">
-        <v>5159</v>
+        <v>1296</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -859,16 +859,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>4400</v>
+        <v>4304</v>
       </c>
       <c r="B28">
-        <v>4404</v>
+        <v>4301</v>
       </c>
       <c r="C28">
-        <v>95.23</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="D28">
-        <v>5159</v>
+        <v>1296</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -876,16 +876,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>4403</v>
+        <v>4108</v>
       </c>
       <c r="B29">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C29">
-        <v>41.59</v>
+        <v>335.6</v>
       </c>
       <c r="D29">
-        <v>5159</v>
+        <v>2122</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -893,67 +893,67 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>4104</v>
+        <v>4108</v>
       </c>
       <c r="B30">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C30">
-        <v>2337.61</v>
+        <v>1488.54</v>
       </c>
       <c r="D30">
-        <v>6151</v>
+        <v>2122</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>4104</v>
+        <v>4301</v>
       </c>
       <c r="B31">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="C31">
-        <v>4390.42</v>
+        <v>369.76</v>
       </c>
       <c r="D31">
-        <v>6151</v>
+        <v>2122</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B32">
         <v>4304</v>
       </c>
       <c r="C32">
-        <v>147.28</v>
+        <v>11007.97</v>
       </c>
       <c r="D32">
-        <v>6151</v>
+        <v>2122</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="B33">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C33">
-        <v>5099.97</v>
+        <v>241.79</v>
       </c>
       <c r="D33">
-        <v>6151</v>
+        <v>4145</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -961,47 +961,47 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B34">
-        <v>4403</v>
+        <v>4104</v>
       </c>
       <c r="C34">
-        <v>193.8</v>
+        <v>12.08</v>
       </c>
       <c r="D34">
-        <v>6151</v>
+        <v>5159</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B35">
-        <v>4100</v>
+        <v>4201</v>
       </c>
       <c r="C35">
-        <v>3632.93</v>
+        <v>479.09</v>
       </c>
       <c r="D35">
-        <v>6151</v>
+        <v>5159</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B36">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="C36">
-        <v>1593.5</v>
+        <v>1640.03</v>
       </c>
       <c r="D36">
         <v>6151</v>
@@ -1012,13 +1012,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>4200</v>
+        <v>4105</v>
       </c>
       <c r="B37">
-        <v>4201</v>
+        <v>4403</v>
       </c>
       <c r="C37">
-        <v>77.97</v>
+        <v>4481.05</v>
       </c>
       <c r="D37">
         <v>6151</v>
@@ -1029,13 +1029,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B38">
-        <v>4302</v>
+        <v>4100</v>
       </c>
       <c r="C38">
-        <v>3073.24</v>
+        <v>3750.58</v>
       </c>
       <c r="D38">
         <v>6151</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="B39">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C39">
-        <v>3814.31</v>
+        <v>884.02</v>
       </c>
       <c r="D39">
         <v>6151</v>
@@ -1063,13 +1063,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="B40">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C40">
-        <v>2220.49</v>
+        <v>291.83</v>
       </c>
       <c r="D40">
         <v>6151</v>
@@ -1080,13 +1080,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="B41">
-        <v>4401</v>
+        <v>4201</v>
       </c>
       <c r="C41">
-        <v>10115.7</v>
+        <v>32.95</v>
       </c>
       <c r="D41">
         <v>6151</v>
@@ -1097,13 +1097,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="B42">
-        <v>4404</v>
+        <v>4302</v>
       </c>
       <c r="C42">
-        <v>896.65</v>
+        <v>808.15</v>
       </c>
       <c r="D42">
         <v>6151</v>
@@ -1114,135 +1114,135 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B43">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C43">
-        <v>255.43</v>
+        <v>98.66</v>
       </c>
       <c r="D43">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B44">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="C44">
-        <v>498.41</v>
+        <v>2091.44</v>
       </c>
       <c r="D44">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="B45">
-        <v>4301</v>
+        <v>4302</v>
       </c>
       <c r="C45">
-        <v>324</v>
+        <v>5914.8</v>
       </c>
       <c r="D45">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="B46">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C46">
-        <v>10968.9</v>
+        <v>3005.7</v>
       </c>
       <c r="D46">
-        <v>7310</v>
+        <v>6151</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="B47">
-        <v>2000</v>
+        <v>4302</v>
       </c>
       <c r="C47">
-        <v>2095.27</v>
+        <v>34.36</v>
       </c>
       <c r="D47">
-        <v>7310</v>
+        <v>6151</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="B48">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C48">
-        <v>8052</v>
+        <v>9863.530000000001</v>
       </c>
       <c r="D48">
-        <v>7310</v>
+        <v>6151</v>
       </c>
       <c r="E48" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="B49">
-        <v>4101</v>
+        <v>4404</v>
       </c>
       <c r="C49">
-        <v>3078.08</v>
+        <v>848.8200000000001</v>
       </c>
       <c r="D49">
-        <v>8529</v>
+        <v>6151</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B50">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C50">
-        <v>2793.62</v>
+        <v>27.97</v>
       </c>
       <c r="D50">
-        <v>8529</v>
+        <v>6982</v>
       </c>
       <c r="E50" t="s">
         <v>5</v>
@@ -1250,16 +1250,16 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B51">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="C51">
-        <v>184.8</v>
+        <v>1728.43</v>
       </c>
       <c r="D51">
-        <v>8529</v>
+        <v>6982</v>
       </c>
       <c r="E51" t="s">
         <v>5</v>
@@ -1267,16 +1267,16 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B52">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C52">
-        <v>547.9400000000001</v>
+        <v>519.4299999999999</v>
       </c>
       <c r="D52">
-        <v>8529</v>
+        <v>6982</v>
       </c>
       <c r="E52" t="s">
         <v>5</v>
@@ -1284,16 +1284,16 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>4100</v>
+        <v>4108</v>
       </c>
       <c r="B53">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="C53">
-        <v>5000.46</v>
+        <v>142.46</v>
       </c>
       <c r="D53">
-        <v>13179</v>
+        <v>6982</v>
       </c>
       <c r="E53" t="s">
         <v>5</v>
@@ -1301,16 +1301,16 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B54">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C54">
-        <v>447.26</v>
+        <v>1665.78</v>
       </c>
       <c r="D54">
-        <v>13179</v>
+        <v>6982</v>
       </c>
       <c r="E54" t="s">
         <v>5</v>
@@ -1318,16 +1318,16 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>4104</v>
+        <v>4108</v>
       </c>
       <c r="B55">
-        <v>4301</v>
+        <v>4404</v>
       </c>
       <c r="C55">
-        <v>2904</v>
+        <v>1213.94</v>
       </c>
       <c r="D55">
-        <v>13179</v>
+        <v>6982</v>
       </c>
       <c r="E55" t="s">
         <v>5</v>
@@ -1335,16 +1335,16 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>4105</v>
+        <v>4304</v>
       </c>
       <c r="B56">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="C56">
-        <v>6321.11</v>
+        <v>320.03</v>
       </c>
       <c r="D56">
-        <v>13179</v>
+        <v>6982</v>
       </c>
       <c r="E56" t="s">
         <v>5</v>
@@ -1352,16 +1352,16 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B57">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="C57">
-        <v>6041.6</v>
+        <v>499.95</v>
       </c>
       <c r="D57">
-        <v>13179</v>
+        <v>6982</v>
       </c>
       <c r="E57" t="s">
         <v>5</v>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B58">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="C58">
-        <v>60</v>
+        <v>13692.9</v>
       </c>
       <c r="D58">
-        <v>13179</v>
+        <v>7310</v>
       </c>
       <c r="E58" t="s">
         <v>5</v>
@@ -1386,16 +1386,16 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="B59">
-        <v>4301</v>
+        <v>2000</v>
       </c>
       <c r="C59">
-        <v>8677.34</v>
+        <v>3523.27</v>
       </c>
       <c r="D59">
-        <v>13179</v>
+        <v>7310</v>
       </c>
       <c r="E59" t="s">
         <v>5</v>
@@ -1403,16 +1403,16 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="B60">
         <v>4304</v>
       </c>
       <c r="C60">
-        <v>4327</v>
+        <v>6732</v>
       </c>
       <c r="D60">
-        <v>13179</v>
+        <v>7310</v>
       </c>
       <c r="E60" t="s">
         <v>5</v>
@@ -1420,16 +1420,16 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>4400</v>
+        <v>4108</v>
       </c>
       <c r="B61">
-        <v>4304</v>
+        <v>4404</v>
       </c>
       <c r="C61">
-        <v>1924.31</v>
+        <v>1218</v>
       </c>
       <c r="D61">
-        <v>13179</v>
+        <v>8529</v>
       </c>
       <c r="E61" t="s">
         <v>5</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>4400</v>
+        <v>4301</v>
       </c>
       <c r="B62">
-        <v>4403</v>
+        <v>4304</v>
       </c>
       <c r="C62">
-        <v>4125.72</v>
+        <v>511.94</v>
       </c>
       <c r="D62">
-        <v>13179</v>
+        <v>8529</v>
       </c>
       <c r="E62" t="s">
         <v>5</v>
@@ -1454,50 +1454,50 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B63">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C63">
-        <v>2561.43</v>
+        <v>8096.46</v>
       </c>
       <c r="D63">
-        <v>13490</v>
+        <v>13179</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B64">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="C64">
-        <v>565.36</v>
+        <v>5751.26</v>
       </c>
       <c r="D64">
-        <v>13490</v>
+        <v>13179</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>4301</v>
+        <v>4105</v>
       </c>
       <c r="B65">
-        <v>4201</v>
+        <v>4403</v>
       </c>
       <c r="C65">
-        <v>96.37</v>
+        <v>5361.11</v>
       </c>
       <c r="D65">
-        <v>13678</v>
+        <v>13179</v>
       </c>
       <c r="E65" t="s">
         <v>5</v>
@@ -1508,50 +1508,50 @@
         <v>4108</v>
       </c>
       <c r="B66">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C66">
-        <v>2404.56</v>
+        <v>2441.6</v>
       </c>
       <c r="D66">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B67">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="C67">
-        <v>246</v>
+        <v>29991.97</v>
       </c>
       <c r="D67">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B68">
-        <v>4105</v>
+        <v>4403</v>
       </c>
       <c r="C68">
-        <v>163.76</v>
+        <v>5360.92</v>
       </c>
       <c r="D68">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1559,13 +1559,13 @@
         <v>4108</v>
       </c>
       <c r="B69">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="C69">
-        <v>10.51</v>
+        <v>3391.43</v>
       </c>
       <c r="D69">
-        <v>14248</v>
+        <v>13490</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
@@ -1579,10 +1579,10 @@
         <v>4400</v>
       </c>
       <c r="C70">
-        <v>71.95999999999999</v>
+        <v>815.36</v>
       </c>
       <c r="D70">
-        <v>14248</v>
+        <v>13490</v>
       </c>
       <c r="E70" t="s">
         <v>6</v>
@@ -1590,19 +1590,19 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B71">
-        <v>4401</v>
+        <v>4201</v>
       </c>
       <c r="C71">
-        <v>238.34</v>
+        <v>96.37</v>
       </c>
       <c r="D71">
-        <v>14248</v>
+        <v>13678</v>
       </c>
       <c r="E71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1610,10 +1610,10 @@
         <v>4108</v>
       </c>
       <c r="B72">
-        <v>4403</v>
+        <v>4101</v>
       </c>
       <c r="C72">
-        <v>658.23</v>
+        <v>2824.56</v>
       </c>
       <c r="D72">
         <v>14248</v>
@@ -1627,10 +1627,10 @@
         <v>4108</v>
       </c>
       <c r="B73">
-        <v>4404</v>
+        <v>4104</v>
       </c>
       <c r="C73">
-        <v>64.40000000000001</v>
+        <v>266</v>
       </c>
       <c r="D73">
         <v>14248</v>
@@ -1641,13 +1641,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>4304</v>
+        <v>4108</v>
       </c>
       <c r="B74">
-        <v>4301</v>
+        <v>4105</v>
       </c>
       <c r="C74">
-        <v>139</v>
+        <v>273.76</v>
       </c>
       <c r="D74">
         <v>14248</v>
@@ -1658,47 +1658,47 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>2000</v>
+        <v>4108</v>
       </c>
       <c r="B75">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="C75">
-        <v>24</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="D75">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E75" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="B76">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C76">
-        <v>14.48</v>
+        <v>329</v>
       </c>
       <c r="D76">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>4108</v>
+        <v>2000</v>
       </c>
       <c r="B77">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="C77">
-        <v>526.24</v>
+        <v>36</v>
       </c>
       <c r="D77">
         <v>14654</v>
@@ -1709,13 +1709,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>4200</v>
+        <v>4105</v>
       </c>
       <c r="B78">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C78">
-        <v>867.7</v>
+        <v>154.24</v>
       </c>
       <c r="D78">
         <v>14654</v>
@@ -1726,13 +1726,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B79">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="C79">
-        <v>1361.02</v>
+        <v>250.24</v>
       </c>
       <c r="D79">
         <v>14654</v>
@@ -1746,10 +1746,10 @@
         <v>4200</v>
       </c>
       <c r="B80">
-        <v>4302</v>
+        <v>4201</v>
       </c>
       <c r="C80">
-        <v>153.06</v>
+        <v>11.73</v>
       </c>
       <c r="D80">
         <v>14654</v>
@@ -1760,13 +1760,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="B81">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="C81">
-        <v>696.75</v>
+        <v>565.89</v>
       </c>
       <c r="D81">
         <v>14654</v>
@@ -1777,13 +1777,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>4203</v>
+        <v>4200</v>
       </c>
       <c r="B82">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="C82">
-        <v>598.7</v>
+        <v>702.14</v>
       </c>
       <c r="D82">
         <v>14654</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>4404</v>
+        <v>4200</v>
       </c>
       <c r="B83">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C83">
-        <v>1292.57</v>
+        <v>754.02</v>
       </c>
       <c r="D83">
         <v>14654</v>
@@ -1811,16 +1811,16 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B84">
-        <v>4100</v>
+        <v>4403</v>
       </c>
       <c r="C84">
-        <v>200.52</v>
+        <v>550.7</v>
       </c>
       <c r="D84">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E84" t="s">
         <v>5</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B85">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="C85">
-        <v>1264.08</v>
+        <v>585.53</v>
       </c>
       <c r="D85">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E85" t="s">
         <v>5</v>
@@ -1845,16 +1845,16 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B86">
-        <v>4200</v>
+        <v>4104</v>
       </c>
       <c r="C86">
-        <v>3057.62</v>
+        <v>200.62</v>
       </c>
       <c r="D86">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E86" t="s">
         <v>5</v>
@@ -1862,16 +1862,16 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B87">
-        <v>4203</v>
+        <v>4302</v>
       </c>
       <c r="C87">
-        <v>2088.84</v>
+        <v>2392.31</v>
       </c>
       <c r="D87">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E87" t="s">
         <v>5</v>
@@ -1882,13 +1882,13 @@
         <v>4301</v>
       </c>
       <c r="B88">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="C88">
-        <v>2087.89</v>
+        <v>3347</v>
       </c>
       <c r="D88">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E88" t="s">
         <v>5</v>
@@ -1896,135 +1896,135 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B89">
-        <v>4200</v>
+        <v>4403</v>
       </c>
       <c r="C89">
-        <v>136.09</v>
+        <v>285.48</v>
       </c>
       <c r="D89">
-        <v>15300</v>
+        <v>14654</v>
       </c>
       <c r="E89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>4108</v>
+        <v>4404</v>
       </c>
       <c r="B90">
-        <v>4101</v>
+        <v>4401</v>
       </c>
       <c r="C90">
-        <v>173.2</v>
+        <v>1112.57</v>
       </c>
       <c r="D90">
-        <v>15300</v>
+        <v>14654</v>
       </c>
       <c r="E90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B91">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="C91">
-        <v>41.33</v>
+        <v>2744.52</v>
       </c>
       <c r="D91">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="B92">
-        <v>4200</v>
+        <v>4105</v>
       </c>
       <c r="C92">
-        <v>2.7</v>
+        <v>231.28</v>
       </c>
       <c r="D92">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B93">
-        <v>4201</v>
+        <v>4104</v>
       </c>
       <c r="C93">
-        <v>63</v>
+        <v>1408.08</v>
       </c>
       <c r="D93">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>4401</v>
+        <v>4108</v>
       </c>
       <c r="B94">
-        <v>4404</v>
+        <v>4200</v>
       </c>
       <c r="C94">
-        <v>3.4</v>
+        <v>944.98</v>
       </c>
       <c r="D94">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>4403</v>
+        <v>4201</v>
       </c>
       <c r="B95">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="C95">
-        <v>9.640000000000001</v>
+        <v>313.82</v>
       </c>
       <c r="D95">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>2000</v>
+        <v>4203</v>
       </c>
       <c r="B96">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C96">
-        <v>911.34</v>
+        <v>2279.16</v>
       </c>
       <c r="D96">
-        <v>16336</v>
+        <v>14788</v>
       </c>
       <c r="E96" t="s">
         <v>5</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="B97">
-        <v>4301</v>
+        <v>4104</v>
       </c>
       <c r="C97">
-        <v>8217.41</v>
+        <v>2099.89</v>
       </c>
       <c r="D97">
-        <v>16336</v>
+        <v>14788</v>
       </c>
       <c r="E97" t="s">
         <v>5</v>
@@ -2049,16 +2049,16 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="B98">
-        <v>4304</v>
+        <v>4104</v>
       </c>
       <c r="C98">
-        <v>2413.47</v>
+        <v>468</v>
       </c>
       <c r="D98">
-        <v>16336</v>
+        <v>14788</v>
       </c>
       <c r="E98" t="s">
         <v>5</v>
@@ -2066,16 +2066,16 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>4104</v>
+        <v>4403</v>
       </c>
       <c r="B99">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C99">
-        <v>6800.03</v>
+        <v>851.66</v>
       </c>
       <c r="D99">
-        <v>16336</v>
+        <v>14788</v>
       </c>
       <c r="E99" t="s">
         <v>5</v>
@@ -2083,115 +2083,115 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="B100">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="C100">
-        <v>6703.02</v>
+        <v>200.2</v>
       </c>
       <c r="D100">
-        <v>16336</v>
+        <v>15300</v>
       </c>
       <c r="E100" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="B101">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C101">
-        <v>1431.86</v>
+        <v>63.12</v>
       </c>
       <c r="D101">
-        <v>16336</v>
+        <v>15300</v>
       </c>
       <c r="E101" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B102">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="C102">
-        <v>945.35</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D102">
-        <v>16336</v>
+        <v>15300</v>
       </c>
       <c r="E102" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
+        <v>4301</v>
+      </c>
+      <c r="B103">
         <v>4201</v>
       </c>
-      <c r="B103">
-        <v>4203</v>
-      </c>
       <c r="C103">
-        <v>3932.43</v>
+        <v>63</v>
       </c>
       <c r="D103">
-        <v>16336</v>
+        <v>15300</v>
       </c>
       <c r="E103" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>4302</v>
+        <v>4108</v>
       </c>
       <c r="B104">
-        <v>4304</v>
+        <v>4400</v>
       </c>
       <c r="C104">
-        <v>1859.29</v>
+        <v>38.74</v>
       </c>
       <c r="D104">
-        <v>16336</v>
+        <v>15305</v>
       </c>
       <c r="E104" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>4400</v>
+        <v>4301</v>
       </c>
       <c r="B105">
-        <v>4101</v>
+        <v>4302</v>
       </c>
       <c r="C105">
-        <v>1319.22</v>
+        <v>32.06</v>
       </c>
       <c r="D105">
-        <v>16336</v>
+        <v>15305</v>
       </c>
       <c r="E105" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>4400</v>
+        <v>4100</v>
       </c>
       <c r="B106">
-        <v>4203</v>
+        <v>4301</v>
       </c>
       <c r="C106">
-        <v>1502.9</v>
+        <v>5986.88</v>
       </c>
       <c r="D106">
         <v>16336</v>
@@ -2202,13 +2202,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>4401</v>
+        <v>4104</v>
       </c>
       <c r="B107">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C107">
-        <v>199.27</v>
+        <v>7796.03</v>
       </c>
       <c r="D107">
         <v>16336</v>
@@ -2219,13 +2219,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B108">
-        <v>4101</v>
+        <v>4203</v>
       </c>
       <c r="C108">
-        <v>4898.55</v>
+        <v>2414.28</v>
       </c>
       <c r="D108">
         <v>16336</v>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B109">
-        <v>4108</v>
+        <v>4302</v>
       </c>
       <c r="C109">
-        <v>3631.78</v>
+        <v>3612.71</v>
       </c>
       <c r="D109">
         <v>16336</v>
@@ -2253,13 +2253,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>4404</v>
+        <v>4105</v>
       </c>
       <c r="B110">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="C110">
-        <v>10742.04</v>
+        <v>10471.89</v>
       </c>
       <c r="D110">
         <v>16336</v>
@@ -2273,13 +2273,13 @@
         <v>4108</v>
       </c>
       <c r="B111">
-        <v>4101</v>
+        <v>2000</v>
       </c>
       <c r="C111">
-        <v>25.24</v>
+        <v>1068.66</v>
       </c>
       <c r="D111">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E111" t="s">
         <v>5</v>
@@ -2290,13 +2290,13 @@
         <v>4108</v>
       </c>
       <c r="B112">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="C112">
-        <v>56.93</v>
+        <v>18865.27</v>
       </c>
       <c r="D112">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E112" t="s">
         <v>5</v>
@@ -2307,13 +2307,13 @@
         <v>4108</v>
       </c>
       <c r="B113">
-        <v>4404</v>
+        <v>4304</v>
       </c>
       <c r="C113">
-        <v>155.17</v>
+        <v>14728.11</v>
       </c>
       <c r="D113">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E113" t="s">
         <v>5</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="B114">
         <v>4203</v>
       </c>
       <c r="C114">
-        <v>0.84</v>
+        <v>14847.5</v>
       </c>
       <c r="D114">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E114" t="s">
         <v>5</v>
@@ -2338,16 +2338,16 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B115">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="C115">
-        <v>38.05</v>
+        <v>16542.25</v>
       </c>
       <c r="D115">
-        <v>16984</v>
+        <v>16336</v>
       </c>
       <c r="E115" t="s">
         <v>5</v>
@@ -2355,16 +2355,16 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="B116">
         <v>4203</v>
       </c>
       <c r="C116">
-        <v>66.05</v>
+        <v>4808.26</v>
       </c>
       <c r="D116">
-        <v>16984</v>
+        <v>16336</v>
       </c>
       <c r="E116" t="s">
         <v>5</v>
@@ -2375,13 +2375,13 @@
         <v>4108</v>
       </c>
       <c r="B117">
-        <v>4400</v>
+        <v>4101</v>
       </c>
       <c r="C117">
-        <v>25.42</v>
+        <v>214.24</v>
       </c>
       <c r="D117">
-        <v>16998</v>
+        <v>16407</v>
       </c>
       <c r="E117" t="s">
         <v>5</v>
@@ -2389,16 +2389,16 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="B118">
-        <v>4101</v>
+        <v>4203</v>
       </c>
       <c r="C118">
-        <v>215.35</v>
+        <v>18.84</v>
       </c>
       <c r="D118">
-        <v>18098</v>
+        <v>16407</v>
       </c>
       <c r="E118" t="s">
         <v>5</v>
@@ -2406,16 +2406,16 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B119">
-        <v>4401</v>
+        <v>4302</v>
       </c>
       <c r="C119">
-        <v>362.7</v>
+        <v>45.32</v>
       </c>
       <c r="D119">
-        <v>18098</v>
+        <v>16407</v>
       </c>
       <c r="E119" t="s">
         <v>5</v>
@@ -2426,13 +2426,13 @@
         <v>4108</v>
       </c>
       <c r="B120">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="C120">
-        <v>260.93</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D120">
-        <v>18098</v>
+        <v>16984</v>
       </c>
       <c r="E120" t="s">
         <v>5</v>
@@ -2440,16 +2440,16 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B121">
-        <v>4101</v>
+        <v>4200</v>
       </c>
       <c r="C121">
-        <v>1297.48</v>
+        <v>638.05</v>
       </c>
       <c r="D121">
-        <v>18098</v>
+        <v>16984</v>
       </c>
       <c r="E121" t="s">
         <v>5</v>
@@ -2460,13 +2460,13 @@
         <v>4301</v>
       </c>
       <c r="B122">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="C122">
-        <v>415.94</v>
+        <v>18.05</v>
       </c>
       <c r="D122">
-        <v>18098</v>
+        <v>16984</v>
       </c>
       <c r="E122" t="s">
         <v>5</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
+        <v>4108</v>
+      </c>
+      <c r="B123">
         <v>4400</v>
       </c>
-      <c r="B123">
-        <v>4401</v>
-      </c>
       <c r="C123">
-        <v>120</v>
+        <v>25.42</v>
       </c>
       <c r="D123">
-        <v>18098</v>
+        <v>16998</v>
       </c>
       <c r="E123" t="s">
         <v>5</v>
@@ -2491,47 +2491,47 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>4403</v>
+        <v>4100</v>
       </c>
       <c r="B124">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C124">
-        <v>13.39</v>
+        <v>117.18</v>
       </c>
       <c r="D124">
-        <v>18098</v>
+        <v>19690</v>
       </c>
       <c r="E124" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>4404</v>
+        <v>4105</v>
       </c>
       <c r="B125">
-        <v>4401</v>
+        <v>4403</v>
       </c>
       <c r="C125">
-        <v>1.73</v>
+        <v>32.34</v>
       </c>
       <c r="D125">
-        <v>18098</v>
+        <v>19690</v>
       </c>
       <c r="E125" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>4100</v>
+        <v>4108</v>
       </c>
       <c r="B126">
         <v>4101</v>
       </c>
       <c r="C126">
-        <v>69.18000000000001</v>
+        <v>35.27</v>
       </c>
       <c r="D126">
         <v>19690</v>
@@ -2542,13 +2542,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B127">
-        <v>4403</v>
+        <v>4203</v>
       </c>
       <c r="C127">
-        <v>32.34</v>
+        <v>51.07</v>
       </c>
       <c r="D127">
         <v>19690</v>
@@ -2559,13 +2559,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B128">
-        <v>4101</v>
+        <v>4404</v>
       </c>
       <c r="C128">
-        <v>35.27</v>
+        <v>189.12</v>
       </c>
       <c r="D128">
         <v>19690</v>
@@ -2576,47 +2576,47 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="B129">
-        <v>4404</v>
+        <v>4100</v>
       </c>
       <c r="C129">
-        <v>177.12</v>
+        <v>204.15</v>
       </c>
       <c r="D129">
-        <v>19690</v>
+        <v>20661</v>
       </c>
       <c r="E129" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B130">
-        <v>4101</v>
+        <v>4104</v>
       </c>
       <c r="C130">
-        <v>3378.67</v>
+        <v>129.75</v>
       </c>
       <c r="D130">
-        <v>20308</v>
+        <v>20661</v>
       </c>
       <c r="E130" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="B131">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="C131">
-        <v>30.4</v>
+        <v>585.88</v>
       </c>
       <c r="D131">
         <v>20661</v>
@@ -2627,13 +2627,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="B132">
-        <v>4105</v>
+        <v>4304</v>
       </c>
       <c r="C132">
-        <v>228.81</v>
+        <v>482.18</v>
       </c>
       <c r="D132">
         <v>20661</v>
@@ -2644,13 +2644,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="B133">
-        <v>4108</v>
+        <v>4404</v>
       </c>
       <c r="C133">
-        <v>226.94</v>
+        <v>139.81</v>
       </c>
       <c r="D133">
         <v>20661</v>
@@ -2667,7 +2667,7 @@
         <v>4201</v>
       </c>
       <c r="C134">
-        <v>1.72</v>
+        <v>70.27</v>
       </c>
       <c r="D134">
         <v>20661</v>
@@ -2681,10 +2681,10 @@
         <v>4203</v>
       </c>
       <c r="B135">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="C135">
-        <v>430.37</v>
+        <v>771.0700000000001</v>
       </c>
       <c r="D135">
         <v>20661</v>
@@ -2695,13 +2695,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>4302</v>
+        <v>4203</v>
       </c>
       <c r="B136">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="C136">
-        <v>93.33</v>
+        <v>22.5</v>
       </c>
       <c r="D136">
         <v>20661</v>
@@ -2715,10 +2715,10 @@
         <v>4302</v>
       </c>
       <c r="B137">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="C137">
-        <v>14.4</v>
+        <v>389.03</v>
       </c>
       <c r="D137">
         <v>20661</v>
@@ -2729,13 +2729,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>4302</v>
+        <v>4400</v>
       </c>
       <c r="B138">
-        <v>4108</v>
+        <v>4404</v>
       </c>
       <c r="C138">
-        <v>40.9</v>
+        <v>903.89</v>
       </c>
       <c r="D138">
         <v>20661</v>
@@ -2746,13 +2746,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>4302</v>
+        <v>4403</v>
       </c>
       <c r="B139">
-        <v>4301</v>
+        <v>4404</v>
       </c>
       <c r="C139">
-        <v>195.82</v>
+        <v>1706.21</v>
       </c>
       <c r="D139">
         <v>20661</v>
@@ -2763,67 +2763,67 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>4302</v>
+        <v>4108</v>
       </c>
       <c r="B140">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C140">
-        <v>44.58</v>
+        <v>2852.78</v>
       </c>
       <c r="D140">
-        <v>20661</v>
+        <v>20827</v>
       </c>
       <c r="E140" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141">
-        <v>4400</v>
+        <v>4108</v>
       </c>
       <c r="B141">
-        <v>4401</v>
+        <v>4403</v>
       </c>
       <c r="C141">
-        <v>548.41</v>
+        <v>351.97</v>
       </c>
       <c r="D141">
-        <v>20661</v>
+        <v>20827</v>
       </c>
       <c r="E141" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="B142">
-        <v>4404</v>
+        <v>4304</v>
       </c>
       <c r="C142">
-        <v>379.48</v>
+        <v>144</v>
       </c>
       <c r="D142">
-        <v>20661</v>
+        <v>23081</v>
       </c>
       <c r="E142" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B143">
-        <v>4401</v>
+        <v>4100</v>
       </c>
       <c r="C143">
-        <v>3894.29</v>
+        <v>24.1</v>
       </c>
       <c r="D143">
-        <v>20827</v>
+        <v>23081</v>
       </c>
       <c r="E143" t="s">
         <v>5</v>
@@ -2831,13 +2831,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B144">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="C144">
-        <v>24.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D144">
         <v>23081</v>
@@ -2848,13 +2848,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145">
-        <v>4108</v>
+        <v>4105</v>
       </c>
       <c r="B145">
         <v>4101</v>
       </c>
       <c r="C145">
-        <v>26.05</v>
+        <v>11.9</v>
       </c>
       <c r="D145">
         <v>23081</v>
@@ -2868,10 +2868,10 @@
         <v>4108</v>
       </c>
       <c r="B146">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C146">
-        <v>63.87</v>
+        <v>114.02</v>
       </c>
       <c r="D146">
         <v>23081</v>
@@ -2882,13 +2882,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147">
-        <v>4301</v>
+        <v>4203</v>
       </c>
       <c r="B147">
-        <v>4304</v>
+        <v>4101</v>
       </c>
       <c r="C147">
-        <v>313.94</v>
+        <v>88.67</v>
       </c>
       <c r="D147">
         <v>23081</v>
@@ -2899,13 +2899,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148">
-        <v>4400</v>
+        <v>4203</v>
       </c>
       <c r="B148">
-        <v>4404</v>
+        <v>4302</v>
       </c>
       <c r="C148">
-        <v>57.64</v>
+        <v>266.05</v>
       </c>
       <c r="D148">
         <v>23081</v>
@@ -2916,13 +2916,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149">
-        <v>4401</v>
+        <v>4203</v>
       </c>
       <c r="B149">
-        <v>4404</v>
+        <v>4304</v>
       </c>
       <c r="C149">
-        <v>616.79</v>
+        <v>38.04</v>
       </c>
       <c r="D149">
         <v>23081</v>
@@ -2933,13 +2933,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150">
-        <v>4403</v>
+        <v>4301</v>
       </c>
       <c r="B150">
-        <v>4404</v>
+        <v>4304</v>
       </c>
       <c r="C150">
-        <v>31.03</v>
+        <v>138</v>
       </c>
       <c r="D150">
         <v>23081</v>
@@ -2950,16 +2950,16 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="B151">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C151">
-        <v>553.9400000000001</v>
+        <v>168</v>
       </c>
       <c r="D151">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E151" t="s">
         <v>5</v>
@@ -2967,16 +2967,16 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152">
-        <v>4101</v>
+        <v>4400</v>
       </c>
       <c r="B152">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="C152">
-        <v>312</v>
+        <v>4.97</v>
       </c>
       <c r="D152">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E152" t="s">
         <v>5</v>
@@ -2984,16 +2984,16 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B153">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C153">
-        <v>228</v>
+        <v>219.46</v>
       </c>
       <c r="D153">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E153" t="s">
         <v>5</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="B154">
         <v>4404</v>
       </c>
       <c r="C154">
-        <v>542.24</v>
+        <v>277.33</v>
       </c>
       <c r="D154">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E154" t="s">
         <v>5</v>
@@ -3018,13 +3018,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B155">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="C155">
-        <v>276.59</v>
+        <v>467.79</v>
       </c>
       <c r="D155">
         <v>23401</v>
@@ -3035,13 +3035,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B156">
-        <v>4301</v>
+        <v>4302</v>
       </c>
       <c r="C156">
-        <v>512.49</v>
+        <v>52.12</v>
       </c>
       <c r="D156">
         <v>23401</v>
@@ -3052,13 +3052,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B157">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="C157">
-        <v>1333.17</v>
+        <v>7.72</v>
       </c>
       <c r="D157">
         <v>23401</v>
@@ -3069,13 +3069,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B158">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C158">
-        <v>814.3</v>
+        <v>488.42</v>
       </c>
       <c r="D158">
         <v>23401</v>
@@ -3086,13 +3086,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B159">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="C159">
-        <v>801.23</v>
+        <v>3984.56</v>
       </c>
       <c r="D159">
         <v>23401</v>
@@ -3103,13 +3103,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="B160">
-        <v>4105</v>
+        <v>4404</v>
       </c>
       <c r="C160">
-        <v>84.14</v>
+        <v>509.81</v>
       </c>
       <c r="D160">
         <v>23401</v>
@@ -3120,13 +3120,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161">
-        <v>4203</v>
+        <v>4304</v>
       </c>
       <c r="B161">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="C161">
-        <v>62.37</v>
+        <v>13.2</v>
       </c>
       <c r="D161">
         <v>23401</v>
@@ -3137,19 +3137,19 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>4304</v>
+        <v>4100</v>
       </c>
       <c r="B162">
-        <v>4301</v>
+        <v>4104</v>
       </c>
       <c r="C162">
-        <v>13.2</v>
+        <v>2244</v>
       </c>
       <c r="D162">
-        <v>23401</v>
+        <v>23638</v>
       </c>
       <c r="E162" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3157,10 +3157,10 @@
         <v>4108</v>
       </c>
       <c r="B163">
-        <v>4100</v>
+        <v>4104</v>
       </c>
       <c r="C163">
-        <v>140.37</v>
+        <v>2539.51</v>
       </c>
       <c r="D163">
         <v>23638</v>
@@ -3174,10 +3174,10 @@
         <v>4108</v>
       </c>
       <c r="B164">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C164">
-        <v>0.6899999999999999</v>
+        <v>5297.08</v>
       </c>
       <c r="D164">
         <v>23638</v>
@@ -3191,10 +3191,10 @@
         <v>4108</v>
       </c>
       <c r="B165">
-        <v>4104</v>
+        <v>4302</v>
       </c>
       <c r="C165">
-        <v>542.83</v>
+        <v>436.38</v>
       </c>
       <c r="D165">
         <v>23638</v>
@@ -3208,10 +3208,10 @@
         <v>4108</v>
       </c>
       <c r="B166">
-        <v>4401</v>
+        <v>4304</v>
       </c>
       <c r="C166">
-        <v>1137.89</v>
+        <v>1319.09</v>
       </c>
       <c r="D166">
         <v>23638</v>
@@ -3222,13 +3222,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>4108</v>
+        <v>4201</v>
       </c>
       <c r="B167">
-        <v>4403</v>
+        <v>4200</v>
       </c>
       <c r="C167">
-        <v>969.8099999999999</v>
+        <v>1214.15</v>
       </c>
       <c r="D167">
         <v>23638</v>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B168">
-        <v>4404</v>
+        <v>4200</v>
       </c>
       <c r="C168">
-        <v>1300.47</v>
+        <v>475.82</v>
       </c>
       <c r="D168">
         <v>23638</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>4201</v>
+        <v>4400</v>
       </c>
       <c r="B169">
-        <v>4105</v>
+        <v>4200</v>
       </c>
       <c r="C169">
-        <v>23.48</v>
+        <v>62.1</v>
       </c>
       <c r="D169">
         <v>23638</v>
@@ -3273,13 +3273,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>4201</v>
+        <v>4401</v>
       </c>
       <c r="B170">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="C170">
-        <v>285.62</v>
+        <v>6458.62</v>
       </c>
       <c r="D170">
         <v>23638</v>
@@ -3290,13 +3290,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171">
-        <v>4201</v>
+        <v>4401</v>
       </c>
       <c r="B171">
-        <v>4403</v>
+        <v>4404</v>
       </c>
       <c r="C171">
-        <v>905.05</v>
+        <v>2870.44</v>
       </c>
       <c r="D171">
         <v>23638</v>
@@ -3307,13 +3307,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>4203</v>
+        <v>4403</v>
       </c>
       <c r="B172">
-        <v>4105</v>
+        <v>4101</v>
       </c>
       <c r="C172">
-        <v>595.8200000000001</v>
+        <v>2813.84</v>
       </c>
       <c r="D172">
         <v>23638</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="B173">
-        <v>4401</v>
+        <v>4105</v>
       </c>
       <c r="C173">
-        <v>395.1</v>
+        <v>2242.14</v>
       </c>
       <c r="D173">
         <v>23638</v>
@@ -3341,50 +3341,50 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B174">
-        <v>4404</v>
+        <v>4200</v>
       </c>
       <c r="C174">
-        <v>1140</v>
+        <v>649.84</v>
       </c>
       <c r="D174">
-        <v>24768</v>
+        <v>23638</v>
       </c>
       <c r="E174" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="B175">
-        <v>4104</v>
+        <v>4302</v>
       </c>
       <c r="C175">
-        <v>705.6</v>
+        <v>928.78</v>
       </c>
       <c r="D175">
-        <v>25570</v>
+        <v>23638</v>
       </c>
       <c r="E175" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="B176">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="C176">
-        <v>84.48</v>
+        <v>279.44</v>
       </c>
       <c r="D176">
-        <v>25598</v>
+        <v>24768</v>
       </c>
       <c r="E176" t="s">
         <v>5</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>4104</v>
+        <v>4301</v>
       </c>
       <c r="B177">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="C177">
-        <v>201.75</v>
+        <v>280.8</v>
       </c>
       <c r="D177">
-        <v>25598</v>
+        <v>25570</v>
       </c>
       <c r="E177" t="s">
         <v>5</v>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="B178">
         <v>4401</v>
       </c>
       <c r="C178">
-        <v>109.05</v>
+        <v>24.48</v>
       </c>
       <c r="D178">
         <v>25598</v>
@@ -3426,13 +3426,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>4201</v>
+        <v>4104</v>
       </c>
       <c r="B179">
         <v>4200</v>
       </c>
       <c r="C179">
-        <v>468.4</v>
+        <v>73.67</v>
       </c>
       <c r="D179">
         <v>25598</v>
@@ -3443,13 +3443,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>4201</v>
+        <v>4104</v>
       </c>
       <c r="B180">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="C180">
-        <v>69.55</v>
+        <v>61.86</v>
       </c>
       <c r="D180">
         <v>25598</v>
@@ -3460,13 +3460,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181">
-        <v>4203</v>
+        <v>4104</v>
       </c>
       <c r="B181">
         <v>4401</v>
       </c>
       <c r="C181">
-        <v>173.3</v>
+        <v>175.27</v>
       </c>
       <c r="D181">
         <v>25598</v>
@@ -3477,13 +3477,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182">
-        <v>4302</v>
+        <v>4203</v>
       </c>
       <c r="B182">
-        <v>4401</v>
+        <v>4200</v>
       </c>
       <c r="C182">
-        <v>47.35</v>
+        <v>53.3</v>
       </c>
       <c r="D182">
         <v>25598</v>
@@ -3494,13 +3494,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B183">
-        <v>4401</v>
+        <v>4200</v>
       </c>
       <c r="C183">
-        <v>403.57</v>
+        <v>0.37</v>
       </c>
       <c r="D183">
         <v>25885</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B184">
-        <v>4404</v>
+        <v>4401</v>
       </c>
       <c r="C184">
-        <v>235.55</v>
+        <v>1479.97</v>
       </c>
       <c r="D184">
         <v>25885</v>
@@ -3528,13 +3528,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="B185">
         <v>4403</v>
       </c>
       <c r="C185">
-        <v>532.22</v>
+        <v>592.22</v>
       </c>
       <c r="D185">
         <v>25885</v>
@@ -3548,32 +3548,15 @@
         <v>4108</v>
       </c>
       <c r="B186">
-        <v>4401</v>
+        <v>4404</v>
       </c>
       <c r="C186">
-        <v>764.4</v>
+        <v>259.55</v>
       </c>
       <c r="D186">
         <v>25885</v>
       </c>
       <c r="E186" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187">
-        <v>4301</v>
-      </c>
-      <c r="B187">
-        <v>4200</v>
-      </c>
-      <c r="C187">
-        <v>0.37</v>
-      </c>
-      <c r="D187">
-        <v>25885</v>
-      </c>
-      <c r="E187" t="s">
         <v>5</v>
       </c>
     </row>

--- a/outputs/shipment_summary.xlsx
+++ b/outputs/shipment_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="8">
   <si>
     <t>From</t>
   </si>
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -423,7 +423,7 @@
         <v>2000</v>
       </c>
       <c r="C2">
-        <v>954.96</v>
+        <v>936.87</v>
       </c>
       <c r="D2">
         <v>189</v>
@@ -437,10 +437,10 @@
         <v>4104</v>
       </c>
       <c r="B3">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="C3">
-        <v>1915.22</v>
+        <v>2041.16</v>
       </c>
       <c r="D3">
         <v>189</v>
@@ -451,13 +451,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>4104</v>
+        <v>4108</v>
       </c>
       <c r="B4">
-        <v>4403</v>
+        <v>2000</v>
       </c>
       <c r="C4">
-        <v>947.85</v>
+        <v>242.28</v>
       </c>
       <c r="D4">
         <v>189</v>
@@ -468,13 +468,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B5">
         <v>4200</v>
       </c>
       <c r="C5">
-        <v>1860.76</v>
+        <v>8009.42</v>
       </c>
       <c r="D5">
         <v>189</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B6">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C6">
-        <v>5867.06</v>
+        <v>4057.52</v>
       </c>
       <c r="D6">
         <v>189</v>
@@ -502,13 +502,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B7">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="C7">
-        <v>1198.21</v>
+        <v>844.63</v>
       </c>
       <c r="D7">
         <v>189</v>
@@ -519,13 +519,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>4400</v>
+        <v>4201</v>
       </c>
       <c r="B8">
-        <v>4404</v>
+        <v>4200</v>
       </c>
       <c r="C8">
-        <v>6482.03</v>
+        <v>2914.03</v>
       </c>
       <c r="D8">
         <v>189</v>
@@ -536,16 +536,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="B9">
-        <v>4101</v>
+        <v>4401</v>
       </c>
       <c r="C9">
-        <v>2441.61</v>
+        <v>2270.03</v>
       </c>
       <c r="D9">
-        <v>1167</v>
+        <v>189</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -556,10 +556,10 @@
         <v>4100</v>
       </c>
       <c r="B10">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C10">
-        <v>1081.7</v>
+        <v>1077.58</v>
       </c>
       <c r="D10">
         <v>1167</v>
@@ -570,13 +570,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="B11">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C11">
-        <v>439.2</v>
+        <v>1071.63</v>
       </c>
       <c r="D11">
         <v>1167</v>
@@ -587,13 +587,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>4105</v>
+        <v>4100</v>
       </c>
       <c r="B12">
-        <v>4403</v>
+        <v>4404</v>
       </c>
       <c r="C12">
-        <v>979.4400000000001</v>
+        <v>1242.1</v>
       </c>
       <c r="D12">
         <v>1167</v>
@@ -604,13 +604,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B13">
-        <v>4401</v>
+        <v>4403</v>
       </c>
       <c r="C13">
-        <v>74.69</v>
+        <v>331.2</v>
       </c>
       <c r="D13">
         <v>1167</v>
@@ -621,13 +621,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>4108</v>
+        <v>4105</v>
       </c>
       <c r="B14">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="C14">
-        <v>846.67</v>
+        <v>175.44</v>
       </c>
       <c r="D14">
         <v>1167</v>
@@ -638,13 +638,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B15">
-        <v>4401</v>
+        <v>4404</v>
       </c>
       <c r="C15">
-        <v>682.47</v>
+        <v>213.36</v>
       </c>
       <c r="D15">
         <v>1167</v>
@@ -658,10 +658,10 @@
         <v>4200</v>
       </c>
       <c r="B16">
-        <v>4403</v>
+        <v>4400</v>
       </c>
       <c r="C16">
-        <v>220.42</v>
+        <v>117.67</v>
       </c>
       <c r="D16">
         <v>1167</v>
@@ -672,13 +672,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="B17">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C17">
-        <v>1937.03</v>
+        <v>540.15</v>
       </c>
       <c r="D17">
         <v>1167</v>
@@ -689,13 +689,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>4203</v>
+        <v>4200</v>
       </c>
       <c r="B18">
         <v>4403</v>
       </c>
       <c r="C18">
-        <v>563.35</v>
+        <v>185.07</v>
       </c>
       <c r="D18">
         <v>1167</v>
@@ -706,13 +706,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>4302</v>
+        <v>4201</v>
       </c>
       <c r="B19">
         <v>4403</v>
       </c>
       <c r="C19">
-        <v>463.82</v>
+        <v>1841.03</v>
       </c>
       <c r="D19">
         <v>1167</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="B20">
         <v>4403</v>
       </c>
       <c r="C20">
-        <v>245.63</v>
+        <v>443.35</v>
       </c>
       <c r="D20">
         <v>1167</v>
@@ -740,13 +740,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>4400</v>
+        <v>4302</v>
       </c>
       <c r="B21">
-        <v>4401</v>
+        <v>4403</v>
       </c>
       <c r="C21">
-        <v>43.81</v>
+        <v>403.82</v>
       </c>
       <c r="D21">
         <v>1167</v>
@@ -757,16 +757,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="B22">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="C22">
-        <v>110.4</v>
+        <v>149.63</v>
       </c>
       <c r="D22">
-        <v>1296</v>
+        <v>1167</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -774,13 +774,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="B23">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C23">
-        <v>23.21</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D23">
         <v>1296</v>
@@ -791,13 +791,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>4108</v>
+        <v>4105</v>
       </c>
       <c r="B24">
-        <v>4100</v>
+        <v>4101</v>
       </c>
       <c r="C24">
-        <v>301.15</v>
+        <v>505.5</v>
       </c>
       <c r="D24">
         <v>1296</v>
@@ -811,10 +811,10 @@
         <v>4108</v>
       </c>
       <c r="B25">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="C25">
-        <v>530.83</v>
+        <v>457.15</v>
       </c>
       <c r="D25">
         <v>1296</v>
@@ -825,13 +825,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>4302</v>
+        <v>4108</v>
       </c>
       <c r="B26">
-        <v>2000</v>
+        <v>4101</v>
       </c>
       <c r="C26">
-        <v>271.19</v>
+        <v>338.83</v>
       </c>
       <c r="D26">
         <v>1296</v>
@@ -842,13 +842,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="B27">
         <v>2000</v>
       </c>
       <c r="C27">
-        <v>113.95</v>
+        <v>90.45</v>
       </c>
       <c r="D27">
         <v>1296</v>
@@ -859,13 +859,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="B28">
-        <v>4301</v>
+        <v>2000</v>
       </c>
       <c r="C28">
-        <v>87.65000000000001</v>
+        <v>294.69</v>
       </c>
       <c r="D28">
         <v>1296</v>
@@ -876,16 +876,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>4108</v>
+        <v>4302</v>
       </c>
       <c r="B29">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C29">
-        <v>335.6</v>
+        <v>474.05</v>
       </c>
       <c r="D29">
-        <v>2122</v>
+        <v>1296</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -893,16 +893,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="B30">
-        <v>4200</v>
+        <v>4301</v>
       </c>
       <c r="C30">
-        <v>1488.54</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D30">
-        <v>2122</v>
+        <v>1296</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -910,16 +910,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="B31">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C31">
-        <v>369.76</v>
+        <v>268.76</v>
       </c>
       <c r="D31">
-        <v>2122</v>
+        <v>1296</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="B32">
-        <v>4304</v>
+        <v>4101</v>
       </c>
       <c r="C32">
-        <v>11007.97</v>
+        <v>444.32</v>
       </c>
       <c r="D32">
-        <v>2122</v>
+        <v>1296</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -944,33 +944,33 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B33">
         <v>4101</v>
       </c>
       <c r="C33">
-        <v>241.79</v>
+        <v>249.08</v>
       </c>
       <c r="D33">
-        <v>4145</v>
+        <v>1296</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>4301</v>
+        <v>4404</v>
       </c>
       <c r="B34">
-        <v>4104</v>
+        <v>4101</v>
       </c>
       <c r="C34">
-        <v>12.08</v>
+        <v>55.55</v>
       </c>
       <c r="D34">
-        <v>5159</v>
+        <v>1296</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -978,16 +978,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B35">
-        <v>4201</v>
+        <v>4403</v>
       </c>
       <c r="C35">
-        <v>479.09</v>
+        <v>528.23</v>
       </c>
       <c r="D35">
-        <v>5159</v>
+        <v>2122</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
@@ -995,50 +995,50 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>4104</v>
+        <v>4301</v>
       </c>
       <c r="B36">
-        <v>4302</v>
+        <v>2000</v>
       </c>
       <c r="C36">
-        <v>1640.03</v>
+        <v>377.65</v>
       </c>
       <c r="D36">
-        <v>6151</v>
+        <v>2122</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B37">
-        <v>4403</v>
+        <v>4304</v>
       </c>
       <c r="C37">
-        <v>4481.05</v>
+        <v>16887.97</v>
       </c>
       <c r="D37">
-        <v>6151</v>
+        <v>2122</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B38">
-        <v>4100</v>
+        <v>4104</v>
       </c>
       <c r="C38">
-        <v>3750.58</v>
+        <v>9.9</v>
       </c>
       <c r="D38">
-        <v>6151</v>
+        <v>4145</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
@@ -1046,47 +1046,47 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B39">
-        <v>4101</v>
+        <v>4104</v>
       </c>
       <c r="C39">
-        <v>884.02</v>
+        <v>16.8</v>
       </c>
       <c r="D39">
-        <v>6151</v>
+        <v>5159</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B40">
-        <v>4401</v>
+        <v>4201</v>
       </c>
       <c r="C40">
-        <v>291.83</v>
+        <v>1478.78</v>
       </c>
       <c r="D40">
-        <v>6151</v>
+        <v>5159</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>4200</v>
+        <v>4104</v>
       </c>
       <c r="B41">
-        <v>4201</v>
+        <v>4301</v>
       </c>
       <c r="C41">
-        <v>32.95</v>
+        <v>536.03</v>
       </c>
       <c r="D41">
         <v>6151</v>
@@ -1097,13 +1097,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>4200</v>
+        <v>4105</v>
       </c>
       <c r="B42">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C42">
-        <v>808.15</v>
+        <v>2441.05</v>
       </c>
       <c r="D42">
         <v>6151</v>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B43">
-        <v>4401</v>
+        <v>4100</v>
       </c>
       <c r="C43">
-        <v>98.66</v>
+        <v>3553.95</v>
       </c>
       <c r="D43">
         <v>6151</v>
@@ -1131,13 +1131,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B44">
-        <v>4403</v>
+        <v>4101</v>
       </c>
       <c r="C44">
-        <v>2091.44</v>
+        <v>3292.48</v>
       </c>
       <c r="D44">
         <v>6151</v>
@@ -1148,13 +1148,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>4203</v>
+        <v>4200</v>
       </c>
       <c r="B45">
-        <v>4302</v>
+        <v>4201</v>
       </c>
       <c r="C45">
-        <v>5914.8</v>
+        <v>88.2</v>
       </c>
       <c r="D45">
         <v>6151</v>
@@ -1165,13 +1165,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="B46">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="C46">
-        <v>3005.7</v>
+        <v>1849.91</v>
       </c>
       <c r="D46">
         <v>6151</v>
@@ -1182,13 +1182,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="B47">
-        <v>4302</v>
+        <v>4403</v>
       </c>
       <c r="C47">
-        <v>34.36</v>
+        <v>973.1</v>
       </c>
       <c r="D47">
         <v>6151</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>4400</v>
+        <v>4203</v>
       </c>
       <c r="B48">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C48">
-        <v>9863.530000000001</v>
+        <v>1212.75</v>
       </c>
       <c r="D48">
         <v>6151</v>
@@ -1216,13 +1216,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>4400</v>
+        <v>4203</v>
       </c>
       <c r="B49">
-        <v>4404</v>
+        <v>4301</v>
       </c>
       <c r="C49">
-        <v>848.8200000000001</v>
+        <v>858.48</v>
       </c>
       <c r="D49">
         <v>6151</v>
@@ -1233,81 +1233,81 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>4104</v>
+        <v>4203</v>
       </c>
       <c r="B50">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="C50">
-        <v>27.97</v>
+        <v>3843.57</v>
       </c>
       <c r="D50">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="B51">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C51">
-        <v>1728.43</v>
+        <v>1468.06</v>
       </c>
       <c r="D51">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B52">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C52">
-        <v>519.4299999999999</v>
+        <v>8765.09</v>
       </c>
       <c r="D52">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E52" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B53">
-        <v>4400</v>
+        <v>4404</v>
       </c>
       <c r="C53">
-        <v>142.46</v>
+        <v>987.26</v>
       </c>
       <c r="D53">
-        <v>6982</v>
+        <v>6151</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B54">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C54">
-        <v>1665.78</v>
+        <v>2868.43</v>
       </c>
       <c r="D54">
         <v>6982</v>
@@ -1318,13 +1318,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B55">
-        <v>4404</v>
+        <v>4108</v>
       </c>
       <c r="C55">
-        <v>1213.94</v>
+        <v>1089.96</v>
       </c>
       <c r="D55">
         <v>6982</v>
@@ -1335,13 +1335,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>4304</v>
+        <v>4104</v>
       </c>
       <c r="B56">
         <v>4301</v>
       </c>
       <c r="C56">
-        <v>320.03</v>
+        <v>147.97</v>
       </c>
       <c r="D56">
         <v>6982</v>
@@ -1352,13 +1352,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B57">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="C57">
-        <v>499.95</v>
+        <v>1791.43</v>
       </c>
       <c r="D57">
         <v>6982</v>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>4108</v>
+        <v>4304</v>
       </c>
       <c r="B58">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C58">
-        <v>13692.9</v>
+        <v>260.03</v>
       </c>
       <c r="D58">
-        <v>7310</v>
+        <v>6982</v>
       </c>
       <c r="E58" t="s">
         <v>5</v>
@@ -1386,16 +1386,16 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="B59">
-        <v>2000</v>
+        <v>4404</v>
       </c>
       <c r="C59">
-        <v>3523.27</v>
+        <v>349.42</v>
       </c>
       <c r="D59">
-        <v>7310</v>
+        <v>6982</v>
       </c>
       <c r="E59" t="s">
         <v>5</v>
@@ -1403,16 +1403,16 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="B60">
-        <v>4304</v>
+        <v>4404</v>
       </c>
       <c r="C60">
-        <v>6732</v>
+        <v>110.22</v>
       </c>
       <c r="D60">
-        <v>7310</v>
+        <v>6982</v>
       </c>
       <c r="E60" t="s">
         <v>5</v>
@@ -1420,16 +1420,16 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B61">
         <v>4404</v>
       </c>
       <c r="C61">
-        <v>1218</v>
+        <v>2110.3</v>
       </c>
       <c r="D61">
-        <v>8529</v>
+        <v>6982</v>
       </c>
       <c r="E61" t="s">
         <v>5</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B62">
-        <v>4304</v>
+        <v>4100</v>
       </c>
       <c r="C62">
-        <v>511.94</v>
+        <v>232.91</v>
       </c>
       <c r="D62">
-        <v>8529</v>
+        <v>7310</v>
       </c>
       <c r="E62" t="s">
         <v>5</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="B63">
-        <v>4403</v>
+        <v>2000</v>
       </c>
       <c r="C63">
-        <v>8096.46</v>
+        <v>3523.27</v>
       </c>
       <c r="D63">
-        <v>13179</v>
+        <v>7310</v>
       </c>
       <c r="E63" t="s">
         <v>5</v>
@@ -1471,16 +1471,16 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="B64">
-        <v>4403</v>
+        <v>4304</v>
       </c>
       <c r="C64">
-        <v>5751.26</v>
+        <v>18312</v>
       </c>
       <c r="D64">
-        <v>13179</v>
+        <v>7310</v>
       </c>
       <c r="E64" t="s">
         <v>5</v>
@@ -1488,16 +1488,16 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>4105</v>
+        <v>2000</v>
       </c>
       <c r="B65">
-        <v>4403</v>
+        <v>4301</v>
       </c>
       <c r="C65">
-        <v>5361.11</v>
+        <v>2172</v>
       </c>
       <c r="D65">
-        <v>13179</v>
+        <v>8529</v>
       </c>
       <c r="E65" t="s">
         <v>5</v>
@@ -1505,16 +1505,16 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B66">
-        <v>4403</v>
+        <v>4301</v>
       </c>
       <c r="C66">
-        <v>2441.6</v>
+        <v>171.79</v>
       </c>
       <c r="D66">
-        <v>13179</v>
+        <v>8529</v>
       </c>
       <c r="E66" t="s">
         <v>5</v>
@@ -1522,16 +1522,16 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B67">
         <v>4304</v>
       </c>
       <c r="C67">
-        <v>29991.97</v>
+        <v>2155.94</v>
       </c>
       <c r="D67">
-        <v>13179</v>
+        <v>8529</v>
       </c>
       <c r="E67" t="s">
         <v>5</v>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>4301</v>
+        <v>2000</v>
       </c>
       <c r="B68">
-        <v>4403</v>
+        <v>4304</v>
       </c>
       <c r="C68">
-        <v>5360.92</v>
+        <v>2392.86</v>
       </c>
       <c r="D68">
         <v>13179</v>
@@ -1556,50 +1556,50 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B69">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C69">
-        <v>3391.43</v>
+        <v>6524.46</v>
       </c>
       <c r="D69">
-        <v>13490</v>
+        <v>13179</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B70">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="C70">
-        <v>815.36</v>
+        <v>459.26</v>
       </c>
       <c r="D70">
-        <v>13490</v>
+        <v>13179</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>4301</v>
+        <v>4105</v>
       </c>
       <c r="B71">
-        <v>4201</v>
+        <v>4403</v>
       </c>
       <c r="C71">
-        <v>96.37</v>
+        <v>4329.11</v>
       </c>
       <c r="D71">
-        <v>13678</v>
+        <v>13179</v>
       </c>
       <c r="E71" t="s">
         <v>5</v>
@@ -1610,81 +1610,81 @@
         <v>4108</v>
       </c>
       <c r="B72">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C72">
-        <v>2824.56</v>
+        <v>581.6</v>
       </c>
       <c r="D72">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B73">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="C73">
-        <v>266</v>
+        <v>32999.11</v>
       </c>
       <c r="D73">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B74">
-        <v>4105</v>
+        <v>4403</v>
       </c>
       <c r="C74">
-        <v>273.76</v>
+        <v>6968.92</v>
       </c>
       <c r="D74">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B75">
         <v>4400</v>
       </c>
       <c r="C75">
-        <v>91.95999999999999</v>
+        <v>3273.98</v>
       </c>
       <c r="D75">
-        <v>14248</v>
+        <v>13179</v>
       </c>
       <c r="E75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>4304</v>
+        <v>4108</v>
       </c>
       <c r="B76">
-        <v>4301</v>
+        <v>4404</v>
       </c>
       <c r="C76">
-        <v>329</v>
+        <v>435.95</v>
       </c>
       <c r="D76">
-        <v>14248</v>
+        <v>13490</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
@@ -1692,16 +1692,16 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>2000</v>
+        <v>4108</v>
       </c>
       <c r="B77">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="C77">
-        <v>36</v>
+        <v>117.28</v>
       </c>
       <c r="D77">
-        <v>14654</v>
+        <v>13678</v>
       </c>
       <c r="E77" t="s">
         <v>5</v>
@@ -1709,16 +1709,16 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B78">
-        <v>4403</v>
+        <v>4201</v>
       </c>
       <c r="C78">
-        <v>154.24</v>
+        <v>168.37</v>
       </c>
       <c r="D78">
-        <v>14654</v>
+        <v>13678</v>
       </c>
       <c r="E78" t="s">
         <v>5</v>
@@ -1726,16 +1726,16 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B79">
-        <v>4401</v>
+        <v>4203</v>
       </c>
       <c r="C79">
-        <v>250.24</v>
+        <v>153.69</v>
       </c>
       <c r="D79">
-        <v>14654</v>
+        <v>13678</v>
       </c>
       <c r="E79" t="s">
         <v>5</v>
@@ -1743,16 +1743,16 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>4200</v>
+        <v>4301</v>
       </c>
       <c r="B80">
-        <v>4201</v>
+        <v>4302</v>
       </c>
       <c r="C80">
-        <v>11.73</v>
+        <v>108</v>
       </c>
       <c r="D80">
-        <v>14654</v>
+        <v>13678</v>
       </c>
       <c r="E80" t="s">
         <v>5</v>
@@ -1760,81 +1760,81 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B81">
-        <v>4400</v>
+        <v>4101</v>
       </c>
       <c r="C81">
-        <v>565.89</v>
+        <v>1184.56</v>
       </c>
       <c r="D81">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B82">
-        <v>4401</v>
+        <v>4104</v>
       </c>
       <c r="C82">
-        <v>702.14</v>
+        <v>266</v>
       </c>
       <c r="D82">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E82" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="B83">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="C83">
-        <v>754.02</v>
+        <v>343.76</v>
       </c>
       <c r="D83">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E83" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>4203</v>
+        <v>4304</v>
       </c>
       <c r="B84">
-        <v>4403</v>
+        <v>4301</v>
       </c>
       <c r="C84">
-        <v>550.7</v>
+        <v>349</v>
       </c>
       <c r="D84">
-        <v>14654</v>
+        <v>14248</v>
       </c>
       <c r="E84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>4301</v>
+        <v>4105</v>
       </c>
       <c r="B85">
-        <v>4100</v>
+        <v>4403</v>
       </c>
       <c r="C85">
-        <v>585.53</v>
+        <v>10.24</v>
       </c>
       <c r="D85">
         <v>14654</v>
@@ -1848,10 +1848,10 @@
         <v>4301</v>
       </c>
       <c r="B86">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="C86">
-        <v>200.62</v>
+        <v>981.52</v>
       </c>
       <c r="D86">
         <v>14654</v>
@@ -1865,10 +1865,10 @@
         <v>4301</v>
       </c>
       <c r="B87">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C87">
-        <v>2392.31</v>
+        <v>87.83</v>
       </c>
       <c r="D87">
         <v>14654</v>
@@ -1882,10 +1882,10 @@
         <v>4301</v>
       </c>
       <c r="B88">
-        <v>4304</v>
+        <v>4104</v>
       </c>
       <c r="C88">
-        <v>3347</v>
+        <v>372</v>
       </c>
       <c r="D88">
         <v>14654</v>
@@ -1899,10 +1899,10 @@
         <v>4301</v>
       </c>
       <c r="B89">
-        <v>4403</v>
+        <v>4108</v>
       </c>
       <c r="C89">
-        <v>285.48</v>
+        <v>265.76</v>
       </c>
       <c r="D89">
         <v>14654</v>
@@ -1913,13 +1913,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>4404</v>
+        <v>4301</v>
       </c>
       <c r="B90">
-        <v>4401</v>
+        <v>4201</v>
       </c>
       <c r="C90">
-        <v>1112.57</v>
+        <v>443.26</v>
       </c>
       <c r="D90">
         <v>14654</v>
@@ -1930,16 +1930,16 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="B91">
-        <v>4100</v>
+        <v>4304</v>
       </c>
       <c r="C91">
-        <v>2744.52</v>
+        <v>4255.94</v>
       </c>
       <c r="D91">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E91" t="s">
         <v>5</v>
@@ -1947,16 +1947,16 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="B92">
-        <v>4105</v>
+        <v>4400</v>
       </c>
       <c r="C92">
-        <v>231.28</v>
+        <v>7.56</v>
       </c>
       <c r="D92">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E92" t="s">
         <v>5</v>
@@ -1964,16 +1964,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B93">
-        <v>4104</v>
+        <v>4403</v>
       </c>
       <c r="C93">
-        <v>1408.08</v>
+        <v>163.74</v>
       </c>
       <c r="D93">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E93" t="s">
         <v>5</v>
@@ -1981,16 +1981,16 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B94">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="C94">
-        <v>944.98</v>
+        <v>705.52</v>
       </c>
       <c r="D94">
-        <v>14788</v>
+        <v>14654</v>
       </c>
       <c r="E94" t="s">
         <v>5</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>4201</v>
+        <v>4101</v>
       </c>
       <c r="B95">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C95">
-        <v>313.82</v>
+        <v>674.66</v>
       </c>
       <c r="D95">
         <v>14788</v>
@@ -2015,13 +2015,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>4203</v>
+        <v>4301</v>
       </c>
       <c r="B96">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="C96">
-        <v>2279.16</v>
+        <v>4004.52</v>
       </c>
       <c r="D96">
         <v>14788</v>
@@ -2038,7 +2038,7 @@
         <v>4104</v>
       </c>
       <c r="C97">
-        <v>2099.89</v>
+        <v>4611.97</v>
       </c>
       <c r="D97">
         <v>14788</v>
@@ -2049,13 +2049,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="B98">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="C98">
-        <v>468</v>
+        <v>2487.28</v>
       </c>
       <c r="D98">
         <v>14788</v>
@@ -2066,13 +2066,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>4403</v>
+        <v>4301</v>
       </c>
       <c r="B99">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="C99">
-        <v>851.66</v>
+        <v>502.94</v>
       </c>
       <c r="D99">
         <v>14788</v>
@@ -2083,36 +2083,36 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B100">
-        <v>4101</v>
+        <v>4400</v>
       </c>
       <c r="C100">
-        <v>200.2</v>
+        <v>660.26</v>
       </c>
       <c r="D100">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E100" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B101">
-        <v>4200</v>
+        <v>4401</v>
       </c>
       <c r="C101">
-        <v>63.12</v>
+        <v>167.4</v>
       </c>
       <c r="D101">
-        <v>15300</v>
+        <v>14788</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2120,10 +2120,10 @@
         <v>4108</v>
       </c>
       <c r="B102">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="C102">
-        <v>9.640000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="D102">
         <v>15300</v>
@@ -2151,13 +2151,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B104">
-        <v>4400</v>
+        <v>4201</v>
       </c>
       <c r="C104">
-        <v>38.74</v>
+        <v>33.89</v>
       </c>
       <c r="D104">
         <v>15305</v>
@@ -2174,7 +2174,7 @@
         <v>4302</v>
       </c>
       <c r="C105">
-        <v>32.06</v>
+        <v>59.06</v>
       </c>
       <c r="D105">
         <v>15305</v>
@@ -2185,33 +2185,33 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>4100</v>
+        <v>4108</v>
       </c>
       <c r="B106">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="C106">
-        <v>5986.88</v>
+        <v>10.32</v>
       </c>
       <c r="D106">
-        <v>16336</v>
+        <v>15312</v>
       </c>
       <c r="E106" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>4104</v>
+        <v>4301</v>
       </c>
       <c r="B107">
-        <v>4301</v>
+        <v>4201</v>
       </c>
       <c r="C107">
-        <v>7796.03</v>
+        <v>458.05</v>
       </c>
       <c r="D107">
-        <v>16336</v>
+        <v>15536</v>
       </c>
       <c r="E107" t="s">
         <v>5</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>4105</v>
+        <v>4100</v>
       </c>
       <c r="B108">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="C108">
-        <v>2414.28</v>
+        <v>674.04</v>
       </c>
       <c r="D108">
-        <v>16336</v>
+        <v>15906</v>
       </c>
       <c r="E108" t="s">
         <v>5</v>
@@ -2239,13 +2239,13 @@
         <v>4105</v>
       </c>
       <c r="B109">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C109">
-        <v>3612.71</v>
+        <v>1390.88</v>
       </c>
       <c r="D109">
-        <v>16336</v>
+        <v>15906</v>
       </c>
       <c r="E109" t="s">
         <v>5</v>
@@ -2253,16 +2253,16 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="B110">
-        <v>4304</v>
+        <v>4101</v>
       </c>
       <c r="C110">
-        <v>10471.89</v>
+        <v>480</v>
       </c>
       <c r="D110">
-        <v>16336</v>
+        <v>15906</v>
       </c>
       <c r="E110" t="s">
         <v>5</v>
@@ -2270,16 +2270,16 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B111">
-        <v>2000</v>
+        <v>4101</v>
       </c>
       <c r="C111">
-        <v>1068.66</v>
+        <v>467.64</v>
       </c>
       <c r="D111">
-        <v>16336</v>
+        <v>15906</v>
       </c>
       <c r="E111" t="s">
         <v>5</v>
@@ -2287,16 +2287,16 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B112">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="C112">
-        <v>18865.27</v>
+        <v>188.3</v>
       </c>
       <c r="D112">
-        <v>16336</v>
+        <v>15906</v>
       </c>
       <c r="E112" t="s">
         <v>5</v>
@@ -2304,13 +2304,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>4108</v>
+        <v>4100</v>
       </c>
       <c r="B113">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="C113">
-        <v>14728.11</v>
+        <v>418.88</v>
       </c>
       <c r="D113">
         <v>16336</v>
@@ -2321,13 +2321,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>4200</v>
+        <v>4104</v>
       </c>
       <c r="B114">
-        <v>4203</v>
+        <v>4301</v>
       </c>
       <c r="C114">
-        <v>14847.5</v>
+        <v>2696.03</v>
       </c>
       <c r="D114">
         <v>16336</v>
@@ -2338,13 +2338,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B115">
-        <v>4101</v>
+        <v>2000</v>
       </c>
       <c r="C115">
-        <v>16542.25</v>
+        <v>945.27</v>
       </c>
       <c r="D115">
         <v>16336</v>
@@ -2355,13 +2355,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B116">
-        <v>4203</v>
+        <v>4301</v>
       </c>
       <c r="C116">
-        <v>4808.26</v>
+        <v>12889.61</v>
       </c>
       <c r="D116">
         <v>16336</v>
@@ -2372,16 +2372,16 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B117">
-        <v>4101</v>
+        <v>4203</v>
       </c>
       <c r="C117">
-        <v>214.24</v>
+        <v>11091.5</v>
       </c>
       <c r="D117">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E117" t="s">
         <v>5</v>
@@ -2389,16 +2389,16 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>4301</v>
+        <v>4201</v>
       </c>
       <c r="B118">
         <v>4203</v>
       </c>
       <c r="C118">
-        <v>18.84</v>
+        <v>3485.78</v>
       </c>
       <c r="D118">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E118" t="s">
         <v>5</v>
@@ -2406,16 +2406,16 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>4301</v>
+        <v>4400</v>
       </c>
       <c r="B119">
-        <v>4302</v>
+        <v>4203</v>
       </c>
       <c r="C119">
-        <v>45.32</v>
+        <v>2457.38</v>
       </c>
       <c r="D119">
-        <v>16407</v>
+        <v>16336</v>
       </c>
       <c r="E119" t="s">
         <v>5</v>
@@ -2423,16 +2423,16 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B120">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="C120">
-        <v>9.380000000000001</v>
+        <v>3346.93</v>
       </c>
       <c r="D120">
-        <v>16984</v>
+        <v>16336</v>
       </c>
       <c r="E120" t="s">
         <v>5</v>
@@ -2440,16 +2440,16 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B121">
-        <v>4200</v>
+        <v>4304</v>
       </c>
       <c r="C121">
-        <v>638.05</v>
+        <v>1481.81</v>
       </c>
       <c r="D121">
-        <v>16984</v>
+        <v>16336</v>
       </c>
       <c r="E121" t="s">
         <v>5</v>
@@ -2457,16 +2457,16 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>4301</v>
+        <v>4401</v>
       </c>
       <c r="B122">
-        <v>4203</v>
+        <v>4301</v>
       </c>
       <c r="C122">
-        <v>18.05</v>
+        <v>3543.8</v>
       </c>
       <c r="D122">
-        <v>16984</v>
+        <v>16336</v>
       </c>
       <c r="E122" t="s">
         <v>5</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B123">
-        <v>4400</v>
+        <v>4304</v>
       </c>
       <c r="C123">
-        <v>25.42</v>
+        <v>23578.33</v>
       </c>
       <c r="D123">
-        <v>16998</v>
+        <v>16336</v>
       </c>
       <c r="E123" t="s">
         <v>5</v>
@@ -2491,268 +2491,268 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>4100</v>
+        <v>4404</v>
       </c>
       <c r="B124">
         <v>4101</v>
       </c>
       <c r="C124">
-        <v>117.18</v>
+        <v>6772.15</v>
       </c>
       <c r="D124">
-        <v>19690</v>
+        <v>16336</v>
       </c>
       <c r="E124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>4105</v>
+        <v>4404</v>
       </c>
       <c r="B125">
-        <v>4403</v>
+        <v>4108</v>
       </c>
       <c r="C125">
-        <v>32.34</v>
+        <v>5782.83</v>
       </c>
       <c r="D125">
-        <v>19690</v>
+        <v>16336</v>
       </c>
       <c r="E125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>4108</v>
+        <v>4404</v>
       </c>
       <c r="B126">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C126">
-        <v>35.27</v>
+        <v>2873.05</v>
       </c>
       <c r="D126">
-        <v>19690</v>
+        <v>16336</v>
       </c>
       <c r="E126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B127">
-        <v>4203</v>
+        <v>4105</v>
       </c>
       <c r="C127">
-        <v>51.07</v>
+        <v>44.65</v>
       </c>
       <c r="D127">
-        <v>19690</v>
+        <v>16407</v>
       </c>
       <c r="E127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="B128">
-        <v>4404</v>
+        <v>4302</v>
       </c>
       <c r="C128">
-        <v>189.12</v>
+        <v>45.32</v>
       </c>
       <c r="D128">
-        <v>19690</v>
+        <v>16407</v>
       </c>
       <c r="E128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>4101</v>
+        <v>2000</v>
       </c>
       <c r="B129">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="C129">
-        <v>204.15</v>
+        <v>94.8</v>
       </c>
       <c r="D129">
-        <v>20661</v>
+        <v>16984</v>
       </c>
       <c r="E129" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B130">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="C130">
-        <v>129.75</v>
+        <v>33.38</v>
       </c>
       <c r="D130">
-        <v>20661</v>
+        <v>16984</v>
       </c>
       <c r="E130" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B131">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="C131">
-        <v>585.88</v>
+        <v>16.8</v>
       </c>
       <c r="D131">
-        <v>20661</v>
+        <v>16984</v>
       </c>
       <c r="E131" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B132">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C132">
-        <v>482.18</v>
+        <v>338.05</v>
       </c>
       <c r="D132">
-        <v>20661</v>
+        <v>16984</v>
       </c>
       <c r="E132" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="B133">
-        <v>4404</v>
+        <v>4203</v>
       </c>
       <c r="C133">
-        <v>139.81</v>
+        <v>18.05</v>
       </c>
       <c r="D133">
-        <v>20661</v>
+        <v>16984</v>
       </c>
       <c r="E133" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134">
-        <v>4203</v>
+        <v>4100</v>
       </c>
       <c r="B134">
-        <v>4201</v>
+        <v>4101</v>
       </c>
       <c r="C134">
-        <v>70.27</v>
+        <v>117.18</v>
       </c>
       <c r="D134">
-        <v>20661</v>
+        <v>19690</v>
       </c>
       <c r="E134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135">
-        <v>4203</v>
+        <v>4105</v>
       </c>
       <c r="B135">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="C135">
-        <v>771.0700000000001</v>
+        <v>32.34</v>
       </c>
       <c r="D135">
-        <v>20661</v>
+        <v>19690</v>
       </c>
       <c r="E135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="B136">
-        <v>4304</v>
+        <v>4101</v>
       </c>
       <c r="C136">
-        <v>22.5</v>
+        <v>35.27</v>
       </c>
       <c r="D136">
-        <v>20661</v>
+        <v>19690</v>
       </c>
       <c r="E136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="B137">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="C137">
-        <v>389.03</v>
+        <v>51.07</v>
       </c>
       <c r="D137">
-        <v>20661</v>
+        <v>19690</v>
       </c>
       <c r="E137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>4400</v>
+        <v>4401</v>
       </c>
       <c r="B138">
         <v>4404</v>
       </c>
       <c r="C138">
-        <v>903.89</v>
+        <v>213.12</v>
       </c>
       <c r="D138">
-        <v>20661</v>
+        <v>19690</v>
       </c>
       <c r="E138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>4403</v>
+        <v>4100</v>
       </c>
       <c r="B139">
-        <v>4404</v>
+        <v>4108</v>
       </c>
       <c r="C139">
-        <v>1706.21</v>
+        <v>154.18</v>
       </c>
       <c r="D139">
         <v>20661</v>
@@ -2763,186 +2763,186 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B140">
-        <v>4401</v>
+        <v>4105</v>
       </c>
       <c r="C140">
-        <v>2852.78</v>
+        <v>279.02</v>
       </c>
       <c r="D140">
-        <v>20827</v>
+        <v>20661</v>
       </c>
       <c r="E140" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="B141">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C141">
-        <v>351.97</v>
+        <v>44.17</v>
       </c>
       <c r="D141">
-        <v>20827</v>
+        <v>20661</v>
       </c>
       <c r="E141" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142">
-        <v>2000</v>
+        <v>4101</v>
       </c>
       <c r="B142">
-        <v>4304</v>
+        <v>4404</v>
       </c>
       <c r="C142">
-        <v>144</v>
+        <v>783.97</v>
       </c>
       <c r="D142">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E142" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143">
-        <v>4104</v>
+        <v>4203</v>
       </c>
       <c r="B143">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="C143">
-        <v>24.1</v>
+        <v>149.59</v>
       </c>
       <c r="D143">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E143" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144">
-        <v>4104</v>
+        <v>4301</v>
       </c>
       <c r="B144">
-        <v>4304</v>
+        <v>4105</v>
       </c>
       <c r="C144">
-        <v>65.90000000000001</v>
+        <v>66.83</v>
       </c>
       <c r="D144">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E144" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145">
-        <v>4105</v>
+        <v>4301</v>
       </c>
       <c r="B145">
-        <v>4101</v>
+        <v>4108</v>
       </c>
       <c r="C145">
-        <v>11.9</v>
+        <v>500.01</v>
       </c>
       <c r="D145">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E145" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B146">
-        <v>4101</v>
+        <v>4201</v>
       </c>
       <c r="C146">
-        <v>114.02</v>
+        <v>108.02</v>
       </c>
       <c r="D146">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E146" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147">
-        <v>4203</v>
+        <v>4304</v>
       </c>
       <c r="B147">
-        <v>4101</v>
+        <v>4104</v>
       </c>
       <c r="C147">
-        <v>88.67</v>
+        <v>303.6</v>
       </c>
       <c r="D147">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E147" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148">
-        <v>4203</v>
+        <v>4304</v>
       </c>
       <c r="B148">
-        <v>4302</v>
+        <v>4108</v>
       </c>
       <c r="C148">
-        <v>266.05</v>
+        <v>198.46</v>
       </c>
       <c r="D148">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E148" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149">
-        <v>4203</v>
+        <v>4403</v>
       </c>
       <c r="B149">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C149">
-        <v>38.04</v>
+        <v>1622.21</v>
       </c>
       <c r="D149">
-        <v>23081</v>
+        <v>20661</v>
       </c>
       <c r="E149" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="B150">
-        <v>4304</v>
+        <v>4401</v>
       </c>
       <c r="C150">
-        <v>138</v>
+        <v>358.78</v>
       </c>
       <c r="D150">
-        <v>23081</v>
+        <v>20827</v>
       </c>
       <c r="E150" t="s">
         <v>5</v>
@@ -2950,16 +2950,16 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151">
-        <v>4400</v>
+        <v>4108</v>
       </c>
       <c r="B151">
-        <v>4101</v>
+        <v>4401</v>
       </c>
       <c r="C151">
-        <v>168</v>
+        <v>1213.97</v>
       </c>
       <c r="D151">
-        <v>23081</v>
+        <v>20827</v>
       </c>
       <c r="E151" t="s">
         <v>5</v>
@@ -2967,16 +2967,16 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="B152">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="C152">
-        <v>4.97</v>
+        <v>584.03</v>
       </c>
       <c r="D152">
-        <v>23081</v>
+        <v>20827</v>
       </c>
       <c r="E152" t="s">
         <v>5</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153">
-        <v>4401</v>
+        <v>2000</v>
       </c>
       <c r="B153">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="C153">
-        <v>219.46</v>
+        <v>48</v>
       </c>
       <c r="D153">
         <v>23081</v>
@@ -3001,13 +3001,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154">
-        <v>4401</v>
+        <v>4104</v>
       </c>
       <c r="B154">
-        <v>4404</v>
+        <v>4100</v>
       </c>
       <c r="C154">
-        <v>277.33</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D154">
         <v>23081</v>
@@ -3018,16 +3018,16 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B155">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="C155">
-        <v>467.79</v>
+        <v>24.18</v>
       </c>
       <c r="D155">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E155" t="s">
         <v>5</v>
@@ -3038,13 +3038,13 @@
         <v>4108</v>
       </c>
       <c r="B156">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C156">
-        <v>52.12</v>
+        <v>114.02</v>
       </c>
       <c r="D156">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E156" t="s">
         <v>5</v>
@@ -3052,16 +3052,16 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157">
-        <v>4108</v>
+        <v>4200</v>
       </c>
       <c r="B157">
-        <v>4400</v>
+        <v>4101</v>
       </c>
       <c r="C157">
-        <v>7.72</v>
+        <v>107.54</v>
       </c>
       <c r="D157">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E157" t="s">
         <v>5</v>
@@ -3069,16 +3069,16 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B158">
-        <v>4401</v>
+        <v>4101</v>
       </c>
       <c r="C158">
-        <v>488.42</v>
+        <v>195.67</v>
       </c>
       <c r="D158">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E158" t="s">
         <v>5</v>
@@ -3086,16 +3086,16 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B159">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="C159">
-        <v>3984.56</v>
+        <v>41.82</v>
       </c>
       <c r="D159">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E159" t="s">
         <v>5</v>
@@ -3103,16 +3103,16 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160">
-        <v>4108</v>
+        <v>4203</v>
       </c>
       <c r="B160">
-        <v>4404</v>
+        <v>4302</v>
       </c>
       <c r="C160">
-        <v>509.81</v>
+        <v>251.21</v>
       </c>
       <c r="D160">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E160" t="s">
         <v>5</v>
@@ -3120,16 +3120,16 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161">
+        <v>4203</v>
+      </c>
+      <c r="B161">
         <v>4304</v>
       </c>
-      <c r="B161">
-        <v>4301</v>
-      </c>
       <c r="C161">
-        <v>13.2</v>
+        <v>248.98</v>
       </c>
       <c r="D161">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E161" t="s">
         <v>5</v>
@@ -3137,149 +3137,149 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="B162">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="C162">
-        <v>2244</v>
+        <v>198</v>
       </c>
       <c r="D162">
-        <v>23638</v>
+        <v>23081</v>
       </c>
       <c r="E162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B163">
-        <v>4104</v>
+        <v>4101</v>
       </c>
       <c r="C163">
-        <v>2539.51</v>
+        <v>6.17</v>
       </c>
       <c r="D163">
-        <v>23638</v>
+        <v>23081</v>
       </c>
       <c r="E163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164">
-        <v>4108</v>
+        <v>4400</v>
       </c>
       <c r="B164">
-        <v>4301</v>
+        <v>4403</v>
       </c>
       <c r="C164">
-        <v>5297.08</v>
+        <v>130.8</v>
       </c>
       <c r="D164">
-        <v>23638</v>
+        <v>23081</v>
       </c>
       <c r="E164" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B165">
-        <v>4302</v>
+        <v>4101</v>
       </c>
       <c r="C165">
-        <v>436.38</v>
+        <v>187.81</v>
       </c>
       <c r="D165">
-        <v>23638</v>
+        <v>23081</v>
       </c>
       <c r="E165" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B166">
-        <v>4304</v>
+        <v>4404</v>
       </c>
       <c r="C166">
-        <v>1319.09</v>
+        <v>236.98</v>
       </c>
       <c r="D166">
-        <v>23638</v>
+        <v>23081</v>
       </c>
       <c r="E166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>4201</v>
+        <v>4108</v>
       </c>
       <c r="B167">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="C167">
-        <v>1214.15</v>
+        <v>72</v>
       </c>
       <c r="D167">
-        <v>23638</v>
+        <v>23401</v>
       </c>
       <c r="E167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168">
-        <v>4203</v>
+        <v>4108</v>
       </c>
       <c r="B168">
-        <v>4200</v>
+        <v>4403</v>
       </c>
       <c r="C168">
-        <v>475.82</v>
+        <v>222.56</v>
       </c>
       <c r="D168">
-        <v>23638</v>
+        <v>23401</v>
       </c>
       <c r="E168" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>4400</v>
+        <v>4301</v>
       </c>
       <c r="B169">
-        <v>4200</v>
+        <v>4302</v>
       </c>
       <c r="C169">
-        <v>62.1</v>
+        <v>135.44</v>
       </c>
       <c r="D169">
-        <v>23638</v>
+        <v>23401</v>
       </c>
       <c r="E169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>4401</v>
+        <v>4100</v>
       </c>
       <c r="B170">
-        <v>4101</v>
+        <v>4104</v>
       </c>
       <c r="C170">
-        <v>6458.62</v>
+        <v>1632</v>
       </c>
       <c r="D170">
         <v>23638</v>
@@ -3290,13 +3290,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171">
-        <v>4401</v>
+        <v>4100</v>
       </c>
       <c r="B171">
-        <v>4404</v>
+        <v>4301</v>
       </c>
       <c r="C171">
-        <v>2870.44</v>
+        <v>840</v>
       </c>
       <c r="D171">
         <v>23638</v>
@@ -3307,13 +3307,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B172">
         <v>4101</v>
       </c>
       <c r="C172">
-        <v>2813.84</v>
+        <v>2114.24</v>
       </c>
       <c r="D172">
         <v>23638</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B173">
-        <v>4105</v>
+        <v>4108</v>
       </c>
       <c r="C173">
-        <v>2242.14</v>
+        <v>2323.94</v>
       </c>
       <c r="D173">
         <v>23638</v>
@@ -3341,13 +3341,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B174">
         <v>4200</v>
       </c>
       <c r="C174">
-        <v>649.84</v>
+        <v>275.79</v>
       </c>
       <c r="D174">
         <v>23638</v>
@@ -3358,13 +3358,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175">
-        <v>4403</v>
+        <v>4105</v>
       </c>
       <c r="B175">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="C175">
-        <v>928.78</v>
+        <v>684.09</v>
       </c>
       <c r="D175">
         <v>23638</v>
@@ -3375,138 +3375,138 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>4304</v>
+        <v>4201</v>
       </c>
       <c r="B176">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C176">
-        <v>279.44</v>
+        <v>1154.15</v>
       </c>
       <c r="D176">
-        <v>24768</v>
+        <v>23638</v>
       </c>
       <c r="E176" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>4301</v>
+        <v>4203</v>
       </c>
       <c r="B177">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C177">
-        <v>280.8</v>
+        <v>1315.82</v>
       </c>
       <c r="D177">
-        <v>25570</v>
+        <v>23638</v>
       </c>
       <c r="E177" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>4100</v>
+        <v>4302</v>
       </c>
       <c r="B178">
-        <v>4401</v>
+        <v>4301</v>
       </c>
       <c r="C178">
-        <v>24.48</v>
+        <v>3197.74</v>
       </c>
       <c r="D178">
-        <v>25598</v>
+        <v>23638</v>
       </c>
       <c r="E178" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>4104</v>
+        <v>4304</v>
       </c>
       <c r="B179">
-        <v>4200</v>
+        <v>4301</v>
       </c>
       <c r="C179">
-        <v>73.67</v>
+        <v>2222.11</v>
       </c>
       <c r="D179">
-        <v>25598</v>
+        <v>23638</v>
       </c>
       <c r="E179" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>4104</v>
+        <v>4401</v>
       </c>
       <c r="B180">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="C180">
-        <v>61.86</v>
+        <v>3403.1</v>
       </c>
       <c r="D180">
-        <v>25598</v>
+        <v>23638</v>
       </c>
       <c r="E180" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181">
-        <v>4104</v>
+        <v>4401</v>
       </c>
       <c r="B181">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="C181">
-        <v>175.27</v>
+        <v>9.9</v>
       </c>
       <c r="D181">
-        <v>25598</v>
+        <v>23638</v>
       </c>
       <c r="E181" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182">
-        <v>4203</v>
+        <v>4401</v>
       </c>
       <c r="B182">
-        <v>4200</v>
+        <v>4404</v>
       </c>
       <c r="C182">
-        <v>53.3</v>
+        <v>1456.48</v>
       </c>
       <c r="D182">
-        <v>25598</v>
+        <v>23638</v>
       </c>
       <c r="E182" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B183">
-        <v>4200</v>
+        <v>4101</v>
       </c>
       <c r="C183">
-        <v>0.37</v>
+        <v>6094.6</v>
       </c>
       <c r="D183">
-        <v>25885</v>
+        <v>23638</v>
       </c>
       <c r="E183" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3514,13 +3514,13 @@
         <v>4108</v>
       </c>
       <c r="B184">
-        <v>4401</v>
+        <v>4104</v>
       </c>
       <c r="C184">
-        <v>1479.97</v>
+        <v>26.49</v>
       </c>
       <c r="D184">
-        <v>25885</v>
+        <v>24768</v>
       </c>
       <c r="E184" t="s">
         <v>5</v>
@@ -3528,16 +3528,16 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B185">
-        <v>4403</v>
+        <v>4104</v>
       </c>
       <c r="C185">
-        <v>592.22</v>
+        <v>11.45</v>
       </c>
       <c r="D185">
-        <v>25885</v>
+        <v>24768</v>
       </c>
       <c r="E185" t="s">
         <v>5</v>
@@ -3545,18 +3545,307 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B186">
+        <v>4201</v>
+      </c>
+      <c r="C186">
+        <v>909.11</v>
+      </c>
+      <c r="D186">
+        <v>24768</v>
+      </c>
+      <c r="E186" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187">
+        <v>4108</v>
+      </c>
+      <c r="B187">
+        <v>4200</v>
+      </c>
+      <c r="C187">
+        <v>180</v>
+      </c>
+      <c r="D187">
+        <v>25570</v>
+      </c>
+      <c r="E187" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188">
+        <v>4301</v>
+      </c>
+      <c r="B188">
+        <v>4200</v>
+      </c>
+      <c r="C188">
+        <v>182.69</v>
+      </c>
+      <c r="D188">
+        <v>25570</v>
+      </c>
+      <c r="E188" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189">
+        <v>4301</v>
+      </c>
+      <c r="B189">
+        <v>4304</v>
+      </c>
+      <c r="C189">
+        <v>280.8</v>
+      </c>
+      <c r="D189">
+        <v>25570</v>
+      </c>
+      <c r="E189" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190">
+        <v>4101</v>
+      </c>
+      <c r="B190">
+        <v>4400</v>
+      </c>
+      <c r="C190">
+        <v>200.29</v>
+      </c>
+      <c r="D190">
+        <v>25598</v>
+      </c>
+      <c r="E190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191">
+        <v>4101</v>
+      </c>
+      <c r="B191">
+        <v>4401</v>
+      </c>
+      <c r="C191">
+        <v>463.94</v>
+      </c>
+      <c r="D191">
+        <v>25598</v>
+      </c>
+      <c r="E191" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192">
+        <v>4101</v>
+      </c>
+      <c r="B192">
         <v>4404</v>
       </c>
-      <c r="C186">
-        <v>259.55</v>
-      </c>
-      <c r="D186">
+      <c r="C192">
+        <v>687.97</v>
+      </c>
+      <c r="D192">
+        <v>25598</v>
+      </c>
+      <c r="E192" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193">
+        <v>4301</v>
+      </c>
+      <c r="B193">
+        <v>4100</v>
+      </c>
+      <c r="C193">
+        <v>23.52</v>
+      </c>
+      <c r="D193">
+        <v>25598</v>
+      </c>
+      <c r="E193" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194">
+        <v>4301</v>
+      </c>
+      <c r="B194">
+        <v>4105</v>
+      </c>
+      <c r="C194">
+        <v>191.46</v>
+      </c>
+      <c r="D194">
+        <v>25598</v>
+      </c>
+      <c r="E194" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195">
+        <v>4301</v>
+      </c>
+      <c r="B195">
+        <v>4108</v>
+      </c>
+      <c r="C195">
+        <v>51</v>
+      </c>
+      <c r="D195">
+        <v>25598</v>
+      </c>
+      <c r="E195" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196">
+        <v>4301</v>
+      </c>
+      <c r="B196">
+        <v>4200</v>
+      </c>
+      <c r="C196">
+        <v>1113.11</v>
+      </c>
+      <c r="D196">
+        <v>25598</v>
+      </c>
+      <c r="E196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197">
+        <v>4301</v>
+      </c>
+      <c r="B197">
+        <v>4201</v>
+      </c>
+      <c r="C197">
+        <v>482.05</v>
+      </c>
+      <c r="D197">
+        <v>25598</v>
+      </c>
+      <c r="E197" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198">
+        <v>4301</v>
+      </c>
+      <c r="B198">
+        <v>4203</v>
+      </c>
+      <c r="C198">
+        <v>78.7</v>
+      </c>
+      <c r="D198">
+        <v>25598</v>
+      </c>
+      <c r="E198" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199">
+        <v>4301</v>
+      </c>
+      <c r="B199">
+        <v>4304</v>
+      </c>
+      <c r="C199">
+        <v>184.34</v>
+      </c>
+      <c r="D199">
+        <v>25598</v>
+      </c>
+      <c r="E199" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200">
+        <v>4301</v>
+      </c>
+      <c r="B200">
+        <v>4400</v>
+      </c>
+      <c r="C200">
+        <v>936.55</v>
+      </c>
+      <c r="D200">
+        <v>25598</v>
+      </c>
+      <c r="E200" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201">
+        <v>4301</v>
+      </c>
+      <c r="B201">
+        <v>4403</v>
+      </c>
+      <c r="C201">
+        <v>47.3</v>
+      </c>
+      <c r="D201">
+        <v>25598</v>
+      </c>
+      <c r="E201" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202">
+        <v>4108</v>
+      </c>
+      <c r="B202">
+        <v>4200</v>
+      </c>
+      <c r="C202">
+        <v>0.37</v>
+      </c>
+      <c r="D202">
         <v>25885</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E202" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203">
+        <v>4301</v>
+      </c>
+      <c r="B203">
+        <v>4302</v>
+      </c>
+      <c r="C203">
+        <v>12.37</v>
+      </c>
+      <c r="D203">
+        <v>25885</v>
+      </c>
+      <c r="E203" t="s">
         <v>5</v>
       </c>
     </row>

--- a/outputs/shipment_summary.xlsx
+++ b/outputs/shipment_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="8">
   <si>
     <t>From</t>
   </si>
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3007,7 +3007,7 @@
         <v>4100</v>
       </c>
       <c r="C154">
-        <v>65.81999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="D154">
         <v>23081</v>
@@ -3024,7 +3024,7 @@
         <v>4304</v>
       </c>
       <c r="C155">
-        <v>24.18</v>
+        <v>23.11</v>
       </c>
       <c r="D155">
         <v>23081</v>
@@ -3058,7 +3058,7 @@
         <v>4101</v>
       </c>
       <c r="C157">
-        <v>107.54</v>
+        <v>113.58</v>
       </c>
       <c r="D157">
         <v>23081</v>
@@ -3069,13 +3069,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>4203</v>
+        <v>4201</v>
       </c>
       <c r="B158">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="C158">
-        <v>195.67</v>
+        <v>41.94</v>
       </c>
       <c r="D158">
         <v>23081</v>
@@ -3089,10 +3089,10 @@
         <v>4203</v>
       </c>
       <c r="B159">
-        <v>4105</v>
+        <v>4101</v>
       </c>
       <c r="C159">
-        <v>41.82</v>
+        <v>212.53</v>
       </c>
       <c r="D159">
         <v>23081</v>
@@ -3106,10 +3106,10 @@
         <v>4203</v>
       </c>
       <c r="B160">
-        <v>4302</v>
+        <v>4105</v>
       </c>
       <c r="C160">
-        <v>251.21</v>
+        <v>42.89</v>
       </c>
       <c r="D160">
         <v>23081</v>
@@ -3123,10 +3123,10 @@
         <v>4203</v>
       </c>
       <c r="B161">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="C161">
-        <v>248.98</v>
+        <v>262</v>
       </c>
       <c r="D161">
         <v>23081</v>
@@ -3137,13 +3137,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>4301</v>
+        <v>4203</v>
       </c>
       <c r="B162">
         <v>4304</v>
       </c>
       <c r="C162">
-        <v>198</v>
+        <v>220.26</v>
       </c>
       <c r="D162">
         <v>23081</v>
@@ -3154,13 +3154,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163">
-        <v>4400</v>
+        <v>4301</v>
       </c>
       <c r="B163">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="C163">
-        <v>6.17</v>
+        <v>198</v>
       </c>
       <c r="D163">
         <v>23081</v>
@@ -3174,10 +3174,10 @@
         <v>4400</v>
       </c>
       <c r="B164">
-        <v>4403</v>
+        <v>4101</v>
       </c>
       <c r="C164">
-        <v>130.8</v>
+        <v>3.05</v>
       </c>
       <c r="D164">
         <v>23081</v>
@@ -3188,13 +3188,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="B165">
-        <v>4101</v>
+        <v>4403</v>
       </c>
       <c r="C165">
-        <v>187.81</v>
+        <v>133.92</v>
       </c>
       <c r="D165">
         <v>23081</v>
@@ -3208,10 +3208,10 @@
         <v>4401</v>
       </c>
       <c r="B166">
-        <v>4404</v>
+        <v>4101</v>
       </c>
       <c r="C166">
-        <v>236.98</v>
+        <v>178.82</v>
       </c>
       <c r="D166">
         <v>23081</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>4108</v>
+        <v>4401</v>
       </c>
       <c r="B167">
-        <v>4101</v>
+        <v>4404</v>
       </c>
       <c r="C167">
-        <v>72</v>
+        <v>245.97</v>
       </c>
       <c r="D167">
-        <v>23401</v>
+        <v>23081</v>
       </c>
       <c r="E167" t="s">
         <v>5</v>
@@ -3242,10 +3242,10 @@
         <v>4108</v>
       </c>
       <c r="B168">
-        <v>4403</v>
+        <v>4101</v>
       </c>
       <c r="C168">
-        <v>222.56</v>
+        <v>72</v>
       </c>
       <c r="D168">
         <v>23401</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B169">
-        <v>4302</v>
+        <v>4403</v>
       </c>
       <c r="C169">
-        <v>135.44</v>
+        <v>222.56</v>
       </c>
       <c r="D169">
         <v>23401</v>
@@ -3273,19 +3273,19 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>4100</v>
+        <v>4301</v>
       </c>
       <c r="B170">
-        <v>4104</v>
+        <v>4302</v>
       </c>
       <c r="C170">
-        <v>1632</v>
+        <v>135.44</v>
       </c>
       <c r="D170">
-        <v>23638</v>
+        <v>23401</v>
       </c>
       <c r="E170" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3293,10 +3293,10 @@
         <v>4100</v>
       </c>
       <c r="B171">
-        <v>4301</v>
+        <v>4104</v>
       </c>
       <c r="C171">
-        <v>840</v>
+        <v>1632</v>
       </c>
       <c r="D171">
         <v>23638</v>
@@ -3307,13 +3307,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>4105</v>
+        <v>4100</v>
       </c>
       <c r="B172">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C172">
-        <v>2114.24</v>
+        <v>840</v>
       </c>
       <c r="D172">
         <v>23638</v>
@@ -3327,10 +3327,10 @@
         <v>4105</v>
       </c>
       <c r="B173">
-        <v>4108</v>
+        <v>4101</v>
       </c>
       <c r="C173">
-        <v>2323.94</v>
+        <v>2114.24</v>
       </c>
       <c r="D173">
         <v>23638</v>
@@ -3344,10 +3344,10 @@
         <v>4105</v>
       </c>
       <c r="B174">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="C174">
-        <v>275.79</v>
+        <v>2323.94</v>
       </c>
       <c r="D174">
         <v>23638</v>
@@ -3361,10 +3361,10 @@
         <v>4105</v>
       </c>
       <c r="B175">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C175">
-        <v>684.09</v>
+        <v>275.79</v>
       </c>
       <c r="D175">
         <v>23638</v>
@@ -3375,13 +3375,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>4201</v>
+        <v>4105</v>
       </c>
       <c r="B176">
-        <v>4200</v>
+        <v>4301</v>
       </c>
       <c r="C176">
-        <v>1154.15</v>
+        <v>684.09</v>
       </c>
       <c r="D176">
         <v>23638</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>4203</v>
+        <v>4201</v>
       </c>
       <c r="B177">
         <v>4200</v>
       </c>
       <c r="C177">
-        <v>1315.82</v>
+        <v>1154.15</v>
       </c>
       <c r="D177">
         <v>23638</v>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>4302</v>
+        <v>4203</v>
       </c>
       <c r="B178">
-        <v>4301</v>
+        <v>4200</v>
       </c>
       <c r="C178">
-        <v>3197.74</v>
+        <v>1315.82</v>
       </c>
       <c r="D178">
         <v>23638</v>
@@ -3426,13 +3426,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="B179">
         <v>4301</v>
       </c>
       <c r="C179">
-        <v>2222.11</v>
+        <v>3197.74</v>
       </c>
       <c r="D179">
         <v>23638</v>
@@ -3443,13 +3443,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>4401</v>
+        <v>4304</v>
       </c>
       <c r="B180">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="C180">
-        <v>3403.1</v>
+        <v>2222.11</v>
       </c>
       <c r="D180">
         <v>23638</v>
@@ -3463,10 +3463,10 @@
         <v>4401</v>
       </c>
       <c r="B181">
-        <v>4400</v>
+        <v>4101</v>
       </c>
       <c r="C181">
-        <v>9.9</v>
+        <v>3403.1</v>
       </c>
       <c r="D181">
         <v>23638</v>
@@ -3480,10 +3480,10 @@
         <v>4401</v>
       </c>
       <c r="B182">
-        <v>4404</v>
+        <v>4400</v>
       </c>
       <c r="C182">
-        <v>1456.48</v>
+        <v>9.9</v>
       </c>
       <c r="D182">
         <v>23638</v>
@@ -3494,13 +3494,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183">
-        <v>4403</v>
+        <v>4401</v>
       </c>
       <c r="B183">
-        <v>4101</v>
+        <v>4404</v>
       </c>
       <c r="C183">
-        <v>6094.6</v>
+        <v>1456.48</v>
       </c>
       <c r="D183">
         <v>23638</v>
@@ -3511,30 +3511,30 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184">
-        <v>4108</v>
+        <v>4403</v>
       </c>
       <c r="B184">
-        <v>4104</v>
+        <v>4101</v>
       </c>
       <c r="C184">
-        <v>26.49</v>
+        <v>6094.6</v>
       </c>
       <c r="D184">
-        <v>24768</v>
+        <v>23638</v>
       </c>
       <c r="E184" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B185">
         <v>4104</v>
       </c>
       <c r="C185">
-        <v>11.45</v>
+        <v>26.49</v>
       </c>
       <c r="D185">
         <v>24768</v>
@@ -3548,10 +3548,10 @@
         <v>4301</v>
       </c>
       <c r="B186">
-        <v>4201</v>
+        <v>4104</v>
       </c>
       <c r="C186">
-        <v>909.11</v>
+        <v>11.45</v>
       </c>
       <c r="D186">
         <v>24768</v>
@@ -3562,16 +3562,16 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B187">
-        <v>4200</v>
+        <v>4201</v>
       </c>
       <c r="C187">
-        <v>180</v>
+        <v>909.11</v>
       </c>
       <c r="D187">
-        <v>25570</v>
+        <v>24768</v>
       </c>
       <c r="E187" t="s">
         <v>5</v>
@@ -3579,13 +3579,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B188">
         <v>4200</v>
       </c>
       <c r="C188">
-        <v>182.69</v>
+        <v>180</v>
       </c>
       <c r="D188">
         <v>25570</v>
@@ -3599,10 +3599,10 @@
         <v>4301</v>
       </c>
       <c r="B189">
-        <v>4304</v>
+        <v>4200</v>
       </c>
       <c r="C189">
-        <v>280.8</v>
+        <v>182.69</v>
       </c>
       <c r="D189">
         <v>25570</v>
@@ -3613,16 +3613,16 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="B190">
-        <v>4400</v>
+        <v>4304</v>
       </c>
       <c r="C190">
-        <v>200.29</v>
+        <v>280.8</v>
       </c>
       <c r="D190">
-        <v>25598</v>
+        <v>25570</v>
       </c>
       <c r="E190" t="s">
         <v>5</v>
@@ -3633,10 +3633,10 @@
         <v>4101</v>
       </c>
       <c r="B191">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="C191">
-        <v>463.94</v>
+        <v>200.29</v>
       </c>
       <c r="D191">
         <v>25598</v>
@@ -3650,10 +3650,10 @@
         <v>4101</v>
       </c>
       <c r="B192">
-        <v>4404</v>
+        <v>4401</v>
       </c>
       <c r="C192">
-        <v>687.97</v>
+        <v>463.94</v>
       </c>
       <c r="D192">
         <v>25598</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="B193">
-        <v>4100</v>
+        <v>4404</v>
       </c>
       <c r="C193">
-        <v>23.52</v>
+        <v>687.97</v>
       </c>
       <c r="D193">
         <v>25598</v>
@@ -3684,10 +3684,10 @@
         <v>4301</v>
       </c>
       <c r="B194">
-        <v>4105</v>
+        <v>4100</v>
       </c>
       <c r="C194">
-        <v>191.46</v>
+        <v>23.52</v>
       </c>
       <c r="D194">
         <v>25598</v>
@@ -3701,10 +3701,10 @@
         <v>4301</v>
       </c>
       <c r="B195">
-        <v>4108</v>
+        <v>4105</v>
       </c>
       <c r="C195">
-        <v>51</v>
+        <v>191.46</v>
       </c>
       <c r="D195">
         <v>25598</v>
@@ -3718,10 +3718,10 @@
         <v>4301</v>
       </c>
       <c r="B196">
-        <v>4200</v>
+        <v>4108</v>
       </c>
       <c r="C196">
-        <v>1113.11</v>
+        <v>51</v>
       </c>
       <c r="D196">
         <v>25598</v>
@@ -3735,10 +3735,10 @@
         <v>4301</v>
       </c>
       <c r="B197">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="C197">
-        <v>482.05</v>
+        <v>1113.11</v>
       </c>
       <c r="D197">
         <v>25598</v>
@@ -3752,10 +3752,10 @@
         <v>4301</v>
       </c>
       <c r="B198">
-        <v>4203</v>
+        <v>4201</v>
       </c>
       <c r="C198">
-        <v>78.7</v>
+        <v>482.05</v>
       </c>
       <c r="D198">
         <v>25598</v>
@@ -3769,10 +3769,10 @@
         <v>4301</v>
       </c>
       <c r="B199">
-        <v>4304</v>
+        <v>4203</v>
       </c>
       <c r="C199">
-        <v>184.34</v>
+        <v>78.7</v>
       </c>
       <c r="D199">
         <v>25598</v>
@@ -3786,10 +3786,10 @@
         <v>4301</v>
       </c>
       <c r="B200">
-        <v>4400</v>
+        <v>4304</v>
       </c>
       <c r="C200">
-        <v>936.55</v>
+        <v>184.34</v>
       </c>
       <c r="D200">
         <v>25598</v>
@@ -3803,10 +3803,10 @@
         <v>4301</v>
       </c>
       <c r="B201">
-        <v>4403</v>
+        <v>4400</v>
       </c>
       <c r="C201">
-        <v>47.3</v>
+        <v>936.55</v>
       </c>
       <c r="D201">
         <v>25598</v>
@@ -3817,16 +3817,16 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202">
-        <v>4108</v>
+        <v>4301</v>
       </c>
       <c r="B202">
-        <v>4200</v>
+        <v>4403</v>
       </c>
       <c r="C202">
-        <v>0.37</v>
+        <v>47.3</v>
       </c>
       <c r="D202">
-        <v>25885</v>
+        <v>25598</v>
       </c>
       <c r="E202" t="s">
         <v>5</v>
@@ -3834,19 +3834,104 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203">
-        <v>4301</v>
+        <v>4108</v>
       </c>
       <c r="B203">
-        <v>4302</v>
+        <v>4200</v>
       </c>
       <c r="C203">
-        <v>12.37</v>
+        <v>0.37</v>
       </c>
       <c r="D203">
         <v>25885</v>
       </c>
       <c r="E203" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204">
+        <v>4301</v>
+      </c>
+      <c r="B204">
+        <v>4302</v>
+      </c>
+      <c r="C204">
+        <v>12.37</v>
+      </c>
+      <c r="D204">
+        <v>25885</v>
+      </c>
+      <c r="E204" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205">
+        <v>4101</v>
+      </c>
+      <c r="B205">
+        <v>4302</v>
+      </c>
+      <c r="C205">
+        <v>123.17</v>
+      </c>
+      <c r="D205">
+        <v>26745</v>
+      </c>
+      <c r="E205" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>4105</v>
+      </c>
+      <c r="B206">
+        <v>4200</v>
+      </c>
+      <c r="C206">
+        <v>90.05</v>
+      </c>
+      <c r="D206">
+        <v>26745</v>
+      </c>
+      <c r="E206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>4105</v>
+      </c>
+      <c r="B207">
+        <v>4203</v>
+      </c>
+      <c r="C207">
+        <v>90.05</v>
+      </c>
+      <c r="D207">
+        <v>26745</v>
+      </c>
+      <c r="E207" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208">
+        <v>4105</v>
+      </c>
+      <c r="B208">
+        <v>4302</v>
+      </c>
+      <c r="C208">
+        <v>11.9</v>
+      </c>
+      <c r="D208">
+        <v>26745</v>
+      </c>
+      <c r="E208" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
